--- a/research/traditional_assets/database/data/belgium/belgium_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_healthcare_support_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08807574435978699</v>
+        <v>0.08788930499888753</v>
       </c>
       <c r="C2">
-        <v>1579.215725835649</v>
+        <v>1567.464757282539</v>
       </c>
       <c r="D2">
-        <v>1475.615725835649</v>
+        <v>1480.529757282539</v>
       </c>
       <c r="E2">
-        <v>-400.1</v>
+        <v>-383.435</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.665</v>
       </c>
       <c r="G2">
         <v>103.6</v>
@@ -1457,28 +1457,28 @@
         <v>104.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8382494999999999</v>
       </c>
       <c r="N2">
-        <v>104.3</v>
+        <v>103.4617505</v>
       </c>
       <c r="O2">
-        <v>26.075</v>
+        <v>25.86543762499999</v>
       </c>
       <c r="P2">
-        <v>78.22499999999999</v>
+        <v>77.59631287499998</v>
       </c>
       <c r="Q2">
-        <v>121.125</v>
+        <v>120.496312875</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08807574435978699</v>
+        <v>0.08839601515039144</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738455</v>
+        <v>0.8302756192024353</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>124.4259614828282</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08788930499888753</v>
+        <v>0.08770286563798807</v>
       </c>
       <c r="C3">
-        <v>1567.464757282539</v>
+        <v>1555.746627074761</v>
       </c>
       <c r="D3">
-        <v>1480.529757282539</v>
+        <v>1485.476627074761</v>
       </c>
       <c r="E3">
-        <v>-383.435</v>
+        <v>-366.77</v>
       </c>
       <c r="F3">
-        <v>16.665</v>
+        <v>33.33</v>
       </c>
       <c r="G3">
         <v>103.6</v>
@@ -1539,28 +1539,28 @@
         <v>104.3</v>
       </c>
       <c r="M3">
-        <v>0.8382494999999999</v>
+        <v>1.676499</v>
       </c>
       <c r="N3">
-        <v>103.4617505</v>
+        <v>102.623501</v>
       </c>
       <c r="O3">
-        <v>25.86543762499999</v>
+        <v>25.65587524999999</v>
       </c>
       <c r="P3">
-        <v>77.59631287499998</v>
+        <v>76.96762574999998</v>
       </c>
       <c r="Q3">
-        <v>120.496312875</v>
+        <v>119.86762575</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08839601515039144</v>
+        <v>0.08872282207957966</v>
       </c>
       <c r="T3">
-        <v>0.8302756192024353</v>
+        <v>0.836645694537731</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>124.4259614828282</v>
+        <v>62.2129807414141</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08770286563798807</v>
+        <v>0.08751642627708858</v>
       </c>
       <c r="C4">
-        <v>1555.746627074761</v>
+        <v>1544.061665482517</v>
       </c>
       <c r="D4">
-        <v>1485.476627074761</v>
+        <v>1490.456665482517</v>
       </c>
       <c r="E4">
-        <v>-366.77</v>
+        <v>-350.105</v>
       </c>
       <c r="F4">
-        <v>33.33</v>
+        <v>49.995</v>
       </c>
       <c r="G4">
         <v>103.6</v>
@@ -1621,28 +1621,28 @@
         <v>104.3</v>
       </c>
       <c r="M4">
-        <v>1.676499</v>
+        <v>2.5147485</v>
       </c>
       <c r="N4">
-        <v>102.623501</v>
+        <v>101.7852515</v>
       </c>
       <c r="O4">
-        <v>25.65587524999999</v>
+        <v>25.446312875</v>
       </c>
       <c r="P4">
-        <v>76.96762574999998</v>
+        <v>76.338938625</v>
       </c>
       <c r="Q4">
-        <v>119.86762575</v>
+        <v>119.238938625</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08872282207957966</v>
+        <v>0.08905636729596761</v>
       </c>
       <c r="T4">
-        <v>0.836645694537731</v>
+        <v>0.8431471116325171</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.2129807414141</v>
+        <v>41.47532049427607</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08751642627708858</v>
+        <v>0.08732998691618911</v>
       </c>
       <c r="C5">
-        <v>1544.061665482517</v>
+        <v>1532.410207219807</v>
       </c>
       <c r="D5">
-        <v>1490.456665482517</v>
+        <v>1495.470207219807</v>
       </c>
       <c r="E5">
-        <v>-350.105</v>
+        <v>-333.4400000000001</v>
       </c>
       <c r="F5">
-        <v>49.995</v>
+        <v>66.66</v>
       </c>
       <c r="G5">
         <v>103.6</v>
@@ -1703,28 +1703,28 @@
         <v>104.3</v>
       </c>
       <c r="M5">
-        <v>2.5147485</v>
+        <v>3.352997999999999</v>
       </c>
       <c r="N5">
-        <v>101.7852515</v>
+        <v>100.947002</v>
       </c>
       <c r="O5">
-        <v>25.446312875</v>
+        <v>25.2367505</v>
       </c>
       <c r="P5">
-        <v>76.338938625</v>
+        <v>75.71025149999998</v>
       </c>
       <c r="Q5">
-        <v>119.238938625</v>
+        <v>118.6102515</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08905636729596761</v>
+        <v>0.08939686137103033</v>
       </c>
       <c r="T5">
-        <v>0.8431471116325171</v>
+        <v>0.8497839749167782</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.47532049427607</v>
+        <v>31.10649037070705</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08732998691618911</v>
+        <v>0.08714354755528965</v>
       </c>
       <c r="C6">
-        <v>1532.410207219807</v>
+        <v>1520.792591519428</v>
       </c>
       <c r="D6">
-        <v>1495.470207219807</v>
+        <v>1500.517591519428</v>
       </c>
       <c r="E6">
-        <v>-333.4400000000001</v>
+        <v>-316.775</v>
       </c>
       <c r="F6">
-        <v>66.66</v>
+        <v>83.325</v>
       </c>
       <c r="G6">
         <v>103.6</v>
@@ -1785,28 +1785,28 @@
         <v>104.3</v>
       </c>
       <c r="M6">
-        <v>3.352997999999999</v>
+        <v>4.1912475</v>
       </c>
       <c r="N6">
-        <v>100.947002</v>
+        <v>100.1087525</v>
       </c>
       <c r="O6">
-        <v>25.2367505</v>
+        <v>25.027188125</v>
       </c>
       <c r="P6">
-        <v>75.71025149999998</v>
+        <v>75.08156437499999</v>
       </c>
       <c r="Q6">
-        <v>118.6102515</v>
+        <v>117.981564375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08939686137103033</v>
+        <v>0.08974452374241015</v>
       </c>
       <c r="T6">
-        <v>0.8497839749167782</v>
+        <v>0.8565605616386026</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.10649037070705</v>
+        <v>24.88519229656563</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08714354755528965</v>
+        <v>0.08695710819439018</v>
       </c>
       <c r="C7">
-        <v>1520.792591519428</v>
+        <v>1509.209162209482</v>
       </c>
       <c r="D7">
-        <v>1500.517591519428</v>
+        <v>1505.599162209483</v>
       </c>
       <c r="E7">
-        <v>-316.775</v>
+        <v>-300.11</v>
       </c>
       <c r="F7">
-        <v>83.325</v>
+        <v>99.99000000000001</v>
       </c>
       <c r="G7">
         <v>103.6</v>
@@ -1867,28 +1867,28 @@
         <v>104.3</v>
       </c>
       <c r="M7">
-        <v>4.1912475</v>
+        <v>5.029497</v>
       </c>
       <c r="N7">
-        <v>100.1087525</v>
+        <v>99.27050299999998</v>
       </c>
       <c r="O7">
-        <v>25.027188125</v>
+        <v>24.81762574999999</v>
       </c>
       <c r="P7">
-        <v>75.08156437499999</v>
+        <v>74.45287724999999</v>
       </c>
       <c r="Q7">
-        <v>117.981564375</v>
+        <v>117.35287725</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08974452374241015</v>
+        <v>0.09009958318552147</v>
       </c>
       <c r="T7">
-        <v>0.8565605616386026</v>
+        <v>0.863481331056636</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.88519229656563</v>
+        <v>20.73766024713803</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08695710819439018</v>
+        <v>0.0867706688334907</v>
       </c>
       <c r="C8">
-        <v>1509.209162209482</v>
+        <v>1497.66026779146</v>
       </c>
       <c r="D8">
-        <v>1505.599162209483</v>
+        <v>1510.71526779146</v>
       </c>
       <c r="E8">
-        <v>-300.11</v>
+        <v>-283.4450000000001</v>
       </c>
       <c r="F8">
-        <v>99.98999999999999</v>
+        <v>116.655</v>
       </c>
       <c r="G8">
         <v>103.6</v>
@@ -1949,28 +1949,28 @@
         <v>104.3</v>
       </c>
       <c r="M8">
-        <v>5.029496999999999</v>
+        <v>5.867746499999999</v>
       </c>
       <c r="N8">
-        <v>99.27050299999999</v>
+        <v>98.43225349999999</v>
       </c>
       <c r="O8">
-        <v>24.81762575</v>
+        <v>24.608063375</v>
       </c>
       <c r="P8">
-        <v>74.45287725</v>
+        <v>73.82419012499999</v>
       </c>
       <c r="Q8">
-        <v>117.35287725</v>
+        <v>116.724190125</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09009958318552147</v>
+        <v>0.0904622783155814</v>
       </c>
       <c r="T8">
-        <v>0.863481331056636</v>
+        <v>0.8705509342255948</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.73766024713803</v>
+        <v>17.77513735468974</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08677066883349069</v>
+        <v>0.08658422947259126</v>
       </c>
       <c r="C9">
-        <v>1497.66026779146</v>
+        <v>1486.146261519903</v>
       </c>
       <c r="D9">
-        <v>1510.71526779146</v>
+        <v>1515.866261519903</v>
       </c>
       <c r="E9">
-        <v>-283.445</v>
+        <v>-266.78</v>
       </c>
       <c r="F9">
-        <v>116.655</v>
+        <v>133.32</v>
       </c>
       <c r="G9">
         <v>103.6</v>
@@ -2031,28 +2031,28 @@
         <v>104.3</v>
       </c>
       <c r="M9">
-        <v>5.867746500000001</v>
+        <v>6.705995999999999</v>
       </c>
       <c r="N9">
-        <v>98.43225349999999</v>
+        <v>97.59400399999998</v>
       </c>
       <c r="O9">
-        <v>24.608063375</v>
+        <v>24.398501</v>
       </c>
       <c r="P9">
-        <v>73.82419012499999</v>
+        <v>73.19550299999999</v>
       </c>
       <c r="Q9">
-        <v>116.724190125</v>
+        <v>116.095503</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0904622783155814</v>
+        <v>0.09083285812238179</v>
       </c>
       <c r="T9">
-        <v>0.8705509342255948</v>
+        <v>0.877774224419966</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.77513735468974</v>
+        <v>15.55324518535352</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08658422947259126</v>
+        <v>0.08639779011169178</v>
       </c>
       <c r="C10">
-        <v>1486.146261519903</v>
+        <v>1474.667501483726</v>
       </c>
       <c r="D10">
-        <v>1515.866261519903</v>
+        <v>1521.052501483726</v>
       </c>
       <c r="E10">
-        <v>-266.78</v>
+        <v>-250.115</v>
       </c>
       <c r="F10">
-        <v>133.32</v>
+        <v>149.985</v>
       </c>
       <c r="G10">
         <v>103.6</v>
@@ -2113,28 +2113,28 @@
         <v>104.3</v>
       </c>
       <c r="M10">
-        <v>6.705995999999999</v>
+        <v>7.544245499999999</v>
       </c>
       <c r="N10">
-        <v>97.59400399999998</v>
+        <v>96.75575449999998</v>
       </c>
       <c r="O10">
-        <v>24.398501</v>
+        <v>24.188938625</v>
       </c>
       <c r="P10">
-        <v>73.19550299999999</v>
+        <v>72.56681587499999</v>
       </c>
       <c r="Q10">
-        <v>116.095503</v>
+        <v>115.466815875</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09083285812238179</v>
+        <v>0.09121158254032063</v>
       </c>
       <c r="T10">
-        <v>0.877774224419966</v>
+        <v>0.8851562682449824</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.55324518535352</v>
+        <v>13.82510683142536</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08639779011169178</v>
+        <v>0.08632385075079231</v>
       </c>
       <c r="C11">
-        <v>1474.667501483726</v>
+        <v>1460.06913601522</v>
       </c>
       <c r="D11">
-        <v>1521.052501483726</v>
+        <v>1523.11913601522</v>
       </c>
       <c r="E11">
-        <v>-250.115</v>
+        <v>-233.45</v>
       </c>
       <c r="F11">
-        <v>149.985</v>
+        <v>166.65</v>
       </c>
       <c r="G11">
         <v>103.6</v>
@@ -2195,45 +2195,45 @@
         <v>104.3</v>
       </c>
       <c r="M11">
-        <v>7.544245499999999</v>
+        <v>8.632469999999998</v>
       </c>
       <c r="N11">
-        <v>96.75575449999998</v>
+        <v>95.66752999999999</v>
       </c>
       <c r="O11">
-        <v>24.188938625</v>
+        <v>23.9168825</v>
       </c>
       <c r="P11">
-        <v>72.56681587499999</v>
+        <v>71.75064749999999</v>
       </c>
       <c r="Q11">
-        <v>115.466815875</v>
+        <v>114.6506475</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09121158254032063</v>
+        <v>0.0915987230564359</v>
       </c>
       <c r="T11">
-        <v>0.8851562682449824</v>
+        <v>0.8927023574883326</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.82510683142536</v>
+        <v>12.08228931001208</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08632385075079231</v>
+        <v>0.08614866138989286</v>
       </c>
       <c r="C12">
-        <v>1460.069136015219</v>
+        <v>1448.323236962003</v>
       </c>
       <c r="D12">
-        <v>1523.11913601522</v>
+        <v>1528.038236962003</v>
       </c>
       <c r="E12">
-        <v>-233.45</v>
+        <v>-216.785</v>
       </c>
       <c r="F12">
-        <v>166.65</v>
+        <v>183.315</v>
       </c>
       <c r="G12">
         <v>103.6</v>
@@ -2277,28 +2277,28 @@
         <v>104.3</v>
       </c>
       <c r="M12">
-        <v>8.63247</v>
+        <v>9.495716999999999</v>
       </c>
       <c r="N12">
-        <v>95.66752999999999</v>
+        <v>94.80428299999998</v>
       </c>
       <c r="O12">
-        <v>23.9168825</v>
+        <v>23.70107075</v>
       </c>
       <c r="P12">
-        <v>71.75064749999999</v>
+        <v>71.10321224999998</v>
       </c>
       <c r="Q12">
-        <v>114.6506475</v>
+        <v>114.00321225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0915987230564359</v>
+        <v>0.09199456335943017</v>
       </c>
       <c r="T12">
-        <v>0.8927023574883326</v>
+        <v>0.9004180217708594</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.08228931001208</v>
+        <v>10.98389937273826</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08614866138989286</v>
+        <v>0.08597347202899339</v>
       </c>
       <c r="C13">
-        <v>1448.323236962003</v>
+        <v>1436.609214543704</v>
       </c>
       <c r="D13">
-        <v>1528.038236962003</v>
+        <v>1532.989214543704</v>
       </c>
       <c r="E13">
-        <v>-216.785</v>
+        <v>-200.12</v>
       </c>
       <c r="F13">
-        <v>183.315</v>
+        <v>199.98</v>
       </c>
       <c r="G13">
         <v>103.6</v>
@@ -2359,28 +2359,28 @@
         <v>104.3</v>
       </c>
       <c r="M13">
-        <v>9.495716999999999</v>
+        <v>10.358964</v>
       </c>
       <c r="N13">
-        <v>94.80428299999998</v>
+        <v>93.94103599999998</v>
       </c>
       <c r="O13">
-        <v>23.70107075</v>
+        <v>23.485259</v>
       </c>
       <c r="P13">
-        <v>71.10321224999998</v>
+        <v>70.45577699999998</v>
       </c>
       <c r="Q13">
-        <v>114.00321225</v>
+        <v>113.355777</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09199456335943017</v>
+        <v>0.09239940003294703</v>
       </c>
       <c r="T13">
-        <v>0.9004180217708594</v>
+        <v>0.908309042059807</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.98389937273826</v>
+        <v>10.06857442501007</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08597347202899339</v>
+        <v>0.08596403266809391</v>
       </c>
       <c r="C14">
-        <v>1436.609214543704</v>
+        <v>1420.211888750963</v>
       </c>
       <c r="D14">
-        <v>1532.989214543704</v>
+        <v>1533.256888750963</v>
       </c>
       <c r="E14">
-        <v>-200.12</v>
+        <v>-183.455</v>
       </c>
       <c r="F14">
-        <v>199.98</v>
+        <v>216.645</v>
       </c>
       <c r="G14">
         <v>103.6</v>
@@ -2441,45 +2441,45 @@
         <v>104.3</v>
       </c>
       <c r="M14">
-        <v>10.358964</v>
+        <v>11.5905075</v>
       </c>
       <c r="N14">
-        <v>93.94103599999998</v>
+        <v>92.70949249999998</v>
       </c>
       <c r="O14">
-        <v>23.485259</v>
+        <v>23.177373125</v>
       </c>
       <c r="P14">
-        <v>70.45577699999998</v>
+        <v>69.53211937499998</v>
       </c>
       <c r="Q14">
-        <v>113.355777</v>
+        <v>112.432119375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09239940003294703</v>
+        <v>0.09281354329665967</v>
       </c>
       <c r="T14">
-        <v>0.908309042059807</v>
+        <v>0.9163814651140179</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.06857442501007</v>
+        <v>8.998743152532361</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08596403266809391</v>
+        <v>0.08580159330719443</v>
       </c>
       <c r="C15">
-        <v>1420.211888750963</v>
+        <v>1408.167910001865</v>
       </c>
       <c r="D15">
-        <v>1533.256888750963</v>
+        <v>1537.877910001865</v>
       </c>
       <c r="E15">
-        <v>-183.455</v>
+        <v>-166.79</v>
       </c>
       <c r="F15">
-        <v>216.645</v>
+        <v>233.31</v>
       </c>
       <c r="G15">
         <v>103.6</v>
@@ -2523,28 +2523,28 @@
         <v>104.3</v>
       </c>
       <c r="M15">
-        <v>11.5905075</v>
+        <v>12.482085</v>
       </c>
       <c r="N15">
-        <v>92.70949249999998</v>
+        <v>91.81791499999999</v>
       </c>
       <c r="O15">
-        <v>23.177373125</v>
+        <v>22.95447875</v>
       </c>
       <c r="P15">
-        <v>69.53211937499998</v>
+        <v>68.86343624999999</v>
       </c>
       <c r="Q15">
-        <v>112.432119375</v>
+        <v>111.76343625</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09281354329665967</v>
+        <v>0.0932373177990633</v>
       </c>
       <c r="T15">
-        <v>0.9163814651140179</v>
+        <v>0.9246416189369313</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.998743152532361</v>
+        <v>8.355975784494335</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08580159330719443</v>
+        <v>0.08563915394629498</v>
       </c>
       <c r="C16">
-        <v>1408.167910001865</v>
+        <v>1396.151869675324</v>
       </c>
       <c r="D16">
-        <v>1537.877910001865</v>
+        <v>1542.526869675325</v>
       </c>
       <c r="E16">
-        <v>-166.79</v>
+        <v>-150.125</v>
       </c>
       <c r="F16">
-        <v>233.31</v>
+        <v>249.9750000000001</v>
       </c>
       <c r="G16">
         <v>103.6</v>
@@ -2605,28 +2605,28 @@
         <v>104.3</v>
       </c>
       <c r="M16">
-        <v>12.482085</v>
+        <v>13.3736625</v>
       </c>
       <c r="N16">
-        <v>91.81791499999999</v>
+        <v>90.92633749999999</v>
       </c>
       <c r="O16">
-        <v>22.95447875</v>
+        <v>22.731584375</v>
       </c>
       <c r="P16">
-        <v>68.86343624999999</v>
+        <v>68.19475312499999</v>
       </c>
       <c r="Q16">
-        <v>111.76343625</v>
+        <v>111.094753125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0932373177990633</v>
+        <v>0.09367106346622939</v>
       </c>
       <c r="T16">
-        <v>0.9246416189369313</v>
+        <v>0.9330961293203839</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.355975784494335</v>
+        <v>7.798910732194713</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08563915394629498</v>
+        <v>0.0855727145853955</v>
       </c>
       <c r="C17">
-        <v>1396.151869675325</v>
+        <v>1381.396450905841</v>
       </c>
       <c r="D17">
-        <v>1542.526869675325</v>
+        <v>1544.436450905841</v>
       </c>
       <c r="E17">
-        <v>-150.125</v>
+        <v>-133.46</v>
       </c>
       <c r="F17">
-        <v>249.975</v>
+        <v>266.64</v>
       </c>
       <c r="G17">
         <v>103.6</v>
@@ -2687,45 +2687,45 @@
         <v>104.3</v>
       </c>
       <c r="M17">
-        <v>13.3736625</v>
+        <v>14.478552</v>
       </c>
       <c r="N17">
-        <v>90.92633749999999</v>
+        <v>89.82144799999999</v>
       </c>
       <c r="O17">
-        <v>22.731584375</v>
+        <v>22.455362</v>
       </c>
       <c r="P17">
-        <v>68.19475312499999</v>
+        <v>67.366086</v>
       </c>
       <c r="Q17">
-        <v>111.094753125</v>
+        <v>110.266086</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09367106346622939</v>
+        <v>0.09411513641118513</v>
       </c>
       <c r="T17">
-        <v>0.9330961293203839</v>
+        <v>0.9417519375701091</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.798910732194714</v>
+        <v>7.203759049938143</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0855727145853955</v>
+        <v>0.08541627522449605</v>
       </c>
       <c r="C18">
-        <v>1381.396450905841</v>
+        <v>1369.246513856164</v>
       </c>
       <c r="D18">
-        <v>1544.436450905841</v>
+        <v>1548.951513856164</v>
       </c>
       <c r="E18">
-        <v>-133.46</v>
+        <v>-116.795</v>
       </c>
       <c r="F18">
-        <v>266.64</v>
+        <v>283.305</v>
       </c>
       <c r="G18">
         <v>103.6</v>
@@ -2769,28 +2769,28 @@
         <v>104.3</v>
       </c>
       <c r="M18">
-        <v>14.478552</v>
+        <v>15.3834615</v>
       </c>
       <c r="N18">
-        <v>89.82144799999999</v>
+        <v>88.91653849999999</v>
       </c>
       <c r="O18">
-        <v>22.455362</v>
+        <v>22.229134625</v>
       </c>
       <c r="P18">
-        <v>67.366086</v>
+        <v>66.68740387499999</v>
       </c>
       <c r="Q18">
-        <v>110.266086</v>
+        <v>109.587403875</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09411513641118513</v>
+        <v>0.09456990990903139</v>
       </c>
       <c r="T18">
-        <v>0.9417519375701091</v>
+        <v>0.9506163195125991</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.203759049938143</v>
+        <v>6.780008517588839</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08541627522449605</v>
+        <v>0.08525983586359656</v>
       </c>
       <c r="C19">
-        <v>1369.246513856164</v>
+        <v>1357.123053214445</v>
       </c>
       <c r="D19">
-        <v>1548.951513856164</v>
+        <v>1553.493053214445</v>
       </c>
       <c r="E19">
-        <v>-116.795</v>
+        <v>-100.13</v>
       </c>
       <c r="F19">
-        <v>283.305</v>
+        <v>299.97</v>
       </c>
       <c r="G19">
         <v>103.6</v>
@@ -2851,28 +2851,28 @@
         <v>104.3</v>
       </c>
       <c r="M19">
-        <v>15.3834615</v>
+        <v>16.288371</v>
       </c>
       <c r="N19">
-        <v>88.91653849999999</v>
+        <v>88.01162899999999</v>
       </c>
       <c r="O19">
-        <v>22.229134625</v>
+        <v>22.00290725</v>
       </c>
       <c r="P19">
-        <v>66.68740387499999</v>
+        <v>66.00872174999999</v>
       </c>
       <c r="Q19">
-        <v>109.587403875</v>
+        <v>108.90872175</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09456990990903139</v>
+        <v>0.09503577544341045</v>
       </c>
       <c r="T19">
-        <v>0.9506163195125991</v>
+        <v>0.9596969058927103</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.780008517588839</v>
+        <v>6.403341377722793</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08525983586359658</v>
+        <v>0.08524589650269712</v>
       </c>
       <c r="C20">
-        <v>1357.123053214445</v>
+        <v>1340.864014743386</v>
       </c>
       <c r="D20">
-        <v>1553.493053214445</v>
+        <v>1553.899014743386</v>
       </c>
       <c r="E20">
-        <v>-100.1300000000001</v>
+        <v>-83.46500000000003</v>
       </c>
       <c r="F20">
-        <v>299.97</v>
+        <v>316.635</v>
       </c>
       <c r="G20">
         <v>103.6</v>
@@ -2933,45 +2933,45 @@
         <v>104.3</v>
       </c>
       <c r="M20">
-        <v>16.288371</v>
+        <v>17.5099155</v>
       </c>
       <c r="N20">
-        <v>88.01162899999999</v>
+        <v>86.79008449999998</v>
       </c>
       <c r="O20">
-        <v>22.00290725</v>
+        <v>21.69752112499999</v>
       </c>
       <c r="P20">
-        <v>66.00872174999999</v>
+        <v>65.09256337499998</v>
       </c>
       <c r="Q20">
-        <v>108.90872175</v>
+        <v>107.992563375</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09503577544341045</v>
+        <v>0.09551314383049025</v>
       </c>
       <c r="T20">
-        <v>0.9596969058927103</v>
+        <v>0.9690017042822073</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.403341377722794</v>
+        <v>5.956624976288433</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08524589650269712</v>
+        <v>0.08509695714179764</v>
       </c>
       <c r="C21">
-        <v>1340.864014743386</v>
+        <v>1328.549916728373</v>
       </c>
       <c r="D21">
-        <v>1553.899014743386</v>
+        <v>1558.249916728373</v>
       </c>
       <c r="E21">
-        <v>-83.46500000000003</v>
+        <v>-66.80000000000001</v>
       </c>
       <c r="F21">
-        <v>316.635</v>
+        <v>333.3</v>
       </c>
       <c r="G21">
         <v>103.6</v>
@@ -3015,28 +3015,28 @@
         <v>104.3</v>
       </c>
       <c r="M21">
-        <v>17.5099155</v>
+        <v>18.43149</v>
       </c>
       <c r="N21">
-        <v>86.79008449999998</v>
+        <v>85.86850999999999</v>
       </c>
       <c r="O21">
-        <v>21.69752112499999</v>
+        <v>21.4671275</v>
       </c>
       <c r="P21">
-        <v>65.09256337499998</v>
+        <v>64.40138249999998</v>
       </c>
       <c r="Q21">
-        <v>107.992563375</v>
+        <v>107.3013825</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09551314383049025</v>
+        <v>0.09600244642724705</v>
       </c>
       <c r="T21">
-        <v>0.9690017042822073</v>
+        <v>0.9785391226314416</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.956624976288433</v>
+        <v>5.658793727474013</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08509695714179764</v>
+        <v>0.08494801778089818</v>
       </c>
       <c r="C22">
-        <v>1328.549916728373</v>
+        <v>1316.260252092262</v>
       </c>
       <c r="D22">
-        <v>1558.249916728373</v>
+        <v>1562.625252092262</v>
       </c>
       <c r="E22">
-        <v>-66.80000000000001</v>
+        <v>-50.13499999999999</v>
       </c>
       <c r="F22">
-        <v>333.3</v>
+        <v>349.965</v>
       </c>
       <c r="G22">
         <v>103.6</v>
@@ -3097,28 +3097,28 @@
         <v>104.3</v>
       </c>
       <c r="M22">
-        <v>18.43149</v>
+        <v>19.3530645</v>
       </c>
       <c r="N22">
-        <v>85.86850999999999</v>
+        <v>84.94693549999998</v>
       </c>
       <c r="O22">
-        <v>21.4671275</v>
+        <v>21.236733875</v>
       </c>
       <c r="P22">
-        <v>64.40138249999998</v>
+        <v>63.71020162499998</v>
       </c>
       <c r="Q22">
-        <v>107.3013825</v>
+        <v>106.610201625</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09600244642724705</v>
+        <v>0.09650413643151667</v>
       </c>
       <c r="T22">
-        <v>0.9785391226314416</v>
+        <v>0.9883179946097704</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.658793727474013</v>
+        <v>5.389327359499059</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08494801778089818</v>
+        <v>0.08479907841999869</v>
       </c>
       <c r="C23">
-        <v>1316.260252092262</v>
+        <v>1303.995227230527</v>
       </c>
       <c r="D23">
-        <v>1562.625252092262</v>
+        <v>1567.025227230527</v>
       </c>
       <c r="E23">
-        <v>-50.13500000000005</v>
+        <v>-33.47000000000003</v>
       </c>
       <c r="F23">
-        <v>349.965</v>
+        <v>366.63</v>
       </c>
       <c r="G23">
         <v>103.6</v>
@@ -3179,28 +3179,28 @@
         <v>104.3</v>
       </c>
       <c r="M23">
-        <v>19.3530645</v>
+        <v>20.274639</v>
       </c>
       <c r="N23">
-        <v>84.94693549999998</v>
+        <v>84.02536099999998</v>
       </c>
       <c r="O23">
-        <v>21.236733875</v>
+        <v>21.00634024999999</v>
       </c>
       <c r="P23">
-        <v>63.71020162499998</v>
+        <v>63.01902074999998</v>
       </c>
       <c r="Q23">
-        <v>106.610201625</v>
+        <v>105.91902075</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09650413643151667</v>
+        <v>0.09701869028204961</v>
       </c>
       <c r="T23">
-        <v>0.9883179946097704</v>
+        <v>0.9983476068952358</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.38932735949906</v>
+        <v>5.144357934067283</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08479907841999869</v>
+        <v>0.08465013905909922</v>
       </c>
       <c r="C24">
-        <v>1303.995227230527</v>
+        <v>1291.755050869844</v>
       </c>
       <c r="D24">
-        <v>1567.025227230527</v>
+        <v>1571.450050869844</v>
       </c>
       <c r="E24">
-        <v>-33.47000000000003</v>
+        <v>-16.80500000000001</v>
       </c>
       <c r="F24">
-        <v>366.63</v>
+        <v>383.295</v>
       </c>
       <c r="G24">
         <v>103.6</v>
@@ -3261,28 +3261,28 @@
         <v>104.3</v>
       </c>
       <c r="M24">
-        <v>20.274639</v>
+        <v>21.1962135</v>
       </c>
       <c r="N24">
-        <v>84.02536099999998</v>
+        <v>83.10378649999998</v>
       </c>
       <c r="O24">
-        <v>21.00634024999999</v>
+        <v>20.775946625</v>
       </c>
       <c r="P24">
-        <v>63.01902074999998</v>
+        <v>62.32783987499999</v>
       </c>
       <c r="Q24">
-        <v>105.91902075</v>
+        <v>105.227839875</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09701869028204961</v>
+        <v>0.09754660916766134</v>
       </c>
       <c r="T24">
-        <v>0.9983476068952358</v>
+        <v>1.008637728590714</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.144357934067283</v>
+        <v>4.920690197803489</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08465013905909922</v>
+        <v>0.08450119969819977</v>
       </c>
       <c r="C25">
-        <v>1291.755050869844</v>
+        <v>1279.5399341011</v>
       </c>
       <c r="D25">
-        <v>1571.450050869844</v>
+        <v>1575.8999341011</v>
       </c>
       <c r="E25">
-        <v>-16.80500000000001</v>
+        <v>-0.1399999999999864</v>
       </c>
       <c r="F25">
-        <v>383.295</v>
+        <v>399.96</v>
       </c>
       <c r="G25">
         <v>103.6</v>
@@ -3343,28 +3343,28 @@
         <v>104.3</v>
       </c>
       <c r="M25">
-        <v>21.1962135</v>
+        <v>22.117788</v>
       </c>
       <c r="N25">
-        <v>83.10378649999998</v>
+        <v>82.18221199999998</v>
       </c>
       <c r="O25">
-        <v>20.775946625</v>
+        <v>20.54555299999999</v>
       </c>
       <c r="P25">
-        <v>62.32783987499999</v>
+        <v>61.63665899999998</v>
       </c>
       <c r="Q25">
-        <v>105.227839875</v>
+        <v>104.536659</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09754660916766134</v>
+        <v>0.09808842065552602</v>
       </c>
       <c r="T25">
-        <v>1.008637728590714</v>
+        <v>1.019198642962388</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.920690197803489</v>
+        <v>4.715661439561676</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08450119969819977</v>
+        <v>0.0843522603373003</v>
       </c>
       <c r="C26">
-        <v>1279.5399341011</v>
+        <v>1267.350090412961</v>
       </c>
       <c r="D26">
-        <v>1575.8999341011</v>
+        <v>1580.375090412961</v>
       </c>
       <c r="E26">
-        <v>-0.1400000000000432</v>
+        <v>16.52499999999998</v>
       </c>
       <c r="F26">
-        <v>399.96</v>
+        <v>416.625</v>
       </c>
       <c r="G26">
         <v>103.6</v>
@@ -3425,28 +3425,28 @@
         <v>104.3</v>
       </c>
       <c r="M26">
-        <v>22.117788</v>
+        <v>23.0393625</v>
       </c>
       <c r="N26">
-        <v>82.18221199999998</v>
+        <v>81.26063749999999</v>
       </c>
       <c r="O26">
-        <v>20.54555299999999</v>
+        <v>20.315159375</v>
       </c>
       <c r="P26">
-        <v>61.63665899999998</v>
+        <v>60.94547812499999</v>
       </c>
       <c r="Q26">
-        <v>104.536659</v>
+        <v>103.845478125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09808842065552602</v>
+        <v>0.09864468044973373</v>
       </c>
       <c r="T26">
-        <v>1.019198642962388</v>
+        <v>1.030041181717307</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.715661439561677</v>
+        <v>4.52703498197921</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0843522603373003</v>
+        <v>0.08469082097640084</v>
       </c>
       <c r="C27">
-        <v>1267.350090412961</v>
+        <v>1240.548957428716</v>
       </c>
       <c r="D27">
-        <v>1580.375090412961</v>
+        <v>1570.238957428717</v>
       </c>
       <c r="E27">
-        <v>16.52499999999998</v>
+        <v>33.19</v>
       </c>
       <c r="F27">
-        <v>416.625</v>
+        <v>433.29</v>
       </c>
       <c r="G27">
         <v>103.6</v>
@@ -3507,45 +3507,45 @@
         <v>104.3</v>
       </c>
       <c r="M27">
-        <v>23.0393625</v>
+        <v>25.044162</v>
       </c>
       <c r="N27">
-        <v>81.26063749999999</v>
+        <v>79.25583799999998</v>
       </c>
       <c r="O27">
-        <v>20.315159375</v>
+        <v>19.8139595</v>
       </c>
       <c r="P27">
-        <v>60.94547812499999</v>
+        <v>59.44187849999999</v>
       </c>
       <c r="Q27">
-        <v>103.845478125</v>
+        <v>102.3418785</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09864468044973373</v>
+        <v>0.09921597429243356</v>
       </c>
       <c r="T27">
-        <v>1.030041181717307</v>
+        <v>1.041176762060197</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.52703498197921</v>
+        <v>4.164643241007624</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08469082097640084</v>
+        <v>0.08456063161550137</v>
       </c>
       <c r="C28">
-        <v>1240.548957428716</v>
+        <v>1227.766259624993</v>
       </c>
       <c r="D28">
-        <v>1570.238957428717</v>
+        <v>1574.121259624993</v>
       </c>
       <c r="E28">
-        <v>33.19</v>
+        <v>49.85500000000002</v>
       </c>
       <c r="F28">
-        <v>433.29</v>
+        <v>449.955</v>
       </c>
       <c r="G28">
         <v>103.6</v>
@@ -3589,28 +3589,28 @@
         <v>104.3</v>
       </c>
       <c r="M28">
-        <v>25.044162</v>
+        <v>26.007399</v>
       </c>
       <c r="N28">
-        <v>79.25583799999998</v>
+        <v>78.29260099999998</v>
       </c>
       <c r="O28">
-        <v>19.8139595</v>
+        <v>19.57315024999999</v>
       </c>
       <c r="P28">
-        <v>59.44187849999999</v>
+        <v>58.71945074999998</v>
       </c>
       <c r="Q28">
-        <v>102.3418785</v>
+        <v>101.61945075</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09921597429243356</v>
+        <v>0.09980292002123475</v>
       </c>
       <c r="T28">
-        <v>1.041176762060197</v>
+        <v>1.052617426796042</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.164643241007624</v>
+        <v>4.010397195044378</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08456063161550137</v>
+        <v>0.0851654422546019</v>
       </c>
       <c r="C29">
-        <v>1227.766259624993</v>
+        <v>1193.22626829555</v>
       </c>
       <c r="D29">
-        <v>1574.121259624993</v>
+        <v>1556.24626829555</v>
       </c>
       <c r="E29">
-        <v>49.85500000000002</v>
+        <v>66.52000000000004</v>
       </c>
       <c r="F29">
-        <v>449.955</v>
+        <v>466.6200000000001</v>
       </c>
       <c r="G29">
         <v>103.6</v>
@@ -3671,45 +3671,45 @@
         <v>104.3</v>
       </c>
       <c r="M29">
-        <v>26.007399</v>
+        <v>28.603806</v>
       </c>
       <c r="N29">
-        <v>78.29260099999998</v>
+        <v>75.69619399999998</v>
       </c>
       <c r="O29">
-        <v>19.57315024999999</v>
+        <v>18.92404849999999</v>
       </c>
       <c r="P29">
-        <v>58.71945074999998</v>
+        <v>56.77214549999998</v>
       </c>
       <c r="Q29">
-        <v>101.61945075</v>
+        <v>99.67214549999997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09980292002123475</v>
+        <v>0.1004061697980582</v>
       </c>
       <c r="T29">
-        <v>1.052617426796042</v>
+        <v>1.064375887774551</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.010397195044378</v>
+        <v>3.646367899432683</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0851654422546019</v>
+        <v>0.08506150289370243</v>
       </c>
       <c r="C30">
-        <v>1193.22626829555</v>
+        <v>1179.604219243275</v>
       </c>
       <c r="D30">
-        <v>1556.24626829555</v>
+        <v>1559.289219243275</v>
       </c>
       <c r="E30">
-        <v>66.52000000000004</v>
+        <v>83.18500000000006</v>
       </c>
       <c r="F30">
-        <v>466.6200000000001</v>
+        <v>483.2850000000001</v>
       </c>
       <c r="G30">
         <v>103.6</v>
@@ -3753,28 +3753,28 @@
         <v>104.3</v>
       </c>
       <c r="M30">
-        <v>28.603806</v>
+        <v>29.62537050000001</v>
       </c>
       <c r="N30">
-        <v>75.69619399999998</v>
+        <v>74.67462949999998</v>
       </c>
       <c r="O30">
-        <v>18.92404849999999</v>
+        <v>18.668657375</v>
       </c>
       <c r="P30">
-        <v>56.77214549999998</v>
+        <v>56.00597212499999</v>
       </c>
       <c r="Q30">
-        <v>99.67214549999997</v>
+        <v>98.90597212499998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1004061697980582</v>
+        <v>0.1010264125263415</v>
       </c>
       <c r="T30">
-        <v>1.064375887774551</v>
+        <v>1.076465573005974</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.646367899432683</v>
+        <v>3.520631075314314</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08506150289370243</v>
+        <v>0.08558756353280296</v>
       </c>
       <c r="C31">
-        <v>1179.604219243275</v>
+        <v>1147.659256534396</v>
       </c>
       <c r="D31">
-        <v>1559.289219243275</v>
+        <v>1544.009256534396</v>
       </c>
       <c r="E31">
-        <v>83.18499999999995</v>
+        <v>99.84999999999997</v>
       </c>
       <c r="F31">
-        <v>483.285</v>
+        <v>499.95</v>
       </c>
       <c r="G31">
         <v>103.6</v>
@@ -3835,45 +3835,45 @@
         <v>104.3</v>
       </c>
       <c r="M31">
-        <v>29.6253705</v>
+        <v>32.046795</v>
       </c>
       <c r="N31">
-        <v>74.67462949999998</v>
+        <v>72.25320499999998</v>
       </c>
       <c r="O31">
-        <v>18.668657375</v>
+        <v>18.06330124999999</v>
       </c>
       <c r="P31">
-        <v>56.00597212499999</v>
+        <v>54.18990374999998</v>
       </c>
       <c r="Q31">
-        <v>98.90597212499998</v>
+        <v>97.08990374999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1010264125263415</v>
+        <v>0.1016643764754328</v>
       </c>
       <c r="T31">
-        <v>1.076465573005974</v>
+        <v>1.088900677815439</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.520631075314315</v>
+        <v>3.254615633170181</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08558756353280296</v>
+        <v>0.08550462417190349</v>
       </c>
       <c r="C32">
-        <v>1147.659256534396</v>
+        <v>1133.383398107904</v>
       </c>
       <c r="D32">
-        <v>1544.009256534396</v>
+        <v>1546.398398107904</v>
       </c>
       <c r="E32">
-        <v>99.84999999999997</v>
+        <v>116.515</v>
       </c>
       <c r="F32">
-        <v>499.95</v>
+        <v>516.615</v>
       </c>
       <c r="G32">
         <v>103.6</v>
@@ -3917,28 +3917,28 @@
         <v>104.3</v>
       </c>
       <c r="M32">
-        <v>32.046795</v>
+        <v>33.1150215</v>
       </c>
       <c r="N32">
-        <v>72.25320499999998</v>
+        <v>71.18497849999997</v>
       </c>
       <c r="O32">
-        <v>18.06330124999999</v>
+        <v>17.79624462499999</v>
       </c>
       <c r="P32">
-        <v>54.18990374999998</v>
+        <v>53.38873387499998</v>
       </c>
       <c r="Q32">
-        <v>97.08990374999999</v>
+        <v>96.28873387499998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1016643764754328</v>
+        <v>0.1023208321331935</v>
       </c>
       <c r="T32">
-        <v>1.088900677815439</v>
+        <v>1.101696220445467</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.254615633170181</v>
+        <v>3.149628032100174</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08550462417190349</v>
+        <v>0.08542168481100401</v>
       </c>
       <c r="C33">
-        <v>1133.383398107904</v>
+        <v>1119.114944874693</v>
       </c>
       <c r="D33">
-        <v>1546.398398107904</v>
+        <v>1548.794944874693</v>
       </c>
       <c r="E33">
-        <v>116.515</v>
+        <v>133.1799999999999</v>
       </c>
       <c r="F33">
-        <v>516.615</v>
+        <v>533.28</v>
       </c>
       <c r="G33">
         <v>103.6</v>
@@ -3999,28 +3999,28 @@
         <v>104.3</v>
       </c>
       <c r="M33">
-        <v>33.1150215</v>
+        <v>34.183248</v>
       </c>
       <c r="N33">
-        <v>71.18497849999997</v>
+        <v>70.11675199999999</v>
       </c>
       <c r="O33">
-        <v>17.79624462499999</v>
+        <v>17.529188</v>
       </c>
       <c r="P33">
-        <v>53.38873387499998</v>
+        <v>52.58756399999999</v>
       </c>
       <c r="Q33">
-        <v>96.28873387499998</v>
+        <v>95.48756399999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1023208321331935</v>
+        <v>0.1029965953103</v>
       </c>
       <c r="T33">
-        <v>1.101696220445467</v>
+        <v>1.114868102564615</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.149628032100174</v>
+        <v>3.051202156097045</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08542168481100401</v>
+        <v>0.08726924545010456</v>
       </c>
       <c r="C34">
-        <v>1119.114944874693</v>
+        <v>1050.765898680137</v>
       </c>
       <c r="D34">
-        <v>1548.794944874693</v>
+        <v>1497.110898680137</v>
       </c>
       <c r="E34">
-        <v>133.1799999999999</v>
+        <v>149.845</v>
       </c>
       <c r="F34">
-        <v>533.28</v>
+        <v>549.9450000000001</v>
       </c>
       <c r="G34">
         <v>103.6</v>
@@ -4081,45 +4081,45 @@
         <v>104.3</v>
       </c>
       <c r="M34">
-        <v>34.183248</v>
+        <v>39.54104550000001</v>
       </c>
       <c r="N34">
-        <v>70.11675199999999</v>
+        <v>64.75895449999997</v>
       </c>
       <c r="O34">
-        <v>17.529188</v>
+        <v>16.18973862499999</v>
       </c>
       <c r="P34">
-        <v>52.58756399999999</v>
+        <v>48.56921587499998</v>
       </c>
       <c r="Q34">
-        <v>95.48756399999999</v>
+        <v>91.46921587499997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1029965953103</v>
+        <v>0.1036925305225441</v>
       </c>
       <c r="T34">
-        <v>1.114868102564615</v>
+        <v>1.128433175194781</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.051202156097045</v>
+        <v>2.637765357013637</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08726924545010456</v>
+        <v>0.08724480608920508</v>
       </c>
       <c r="C35">
-        <v>1050.765898680137</v>
+        <v>1034.762047836614</v>
       </c>
       <c r="D35">
-        <v>1497.110898680137</v>
+        <v>1497.772047836614</v>
       </c>
       <c r="E35">
-        <v>149.845</v>
+        <v>166.51</v>
       </c>
       <c r="F35">
-        <v>549.9450000000001</v>
+        <v>566.61</v>
       </c>
       <c r="G35">
         <v>103.6</v>
@@ -4163,28 +4163,28 @@
         <v>104.3</v>
       </c>
       <c r="M35">
-        <v>39.54104550000001</v>
+        <v>40.739259</v>
       </c>
       <c r="N35">
-        <v>64.75895449999997</v>
+        <v>63.56074099999998</v>
       </c>
       <c r="O35">
-        <v>16.18973862499999</v>
+        <v>15.89018524999999</v>
       </c>
       <c r="P35">
-        <v>48.56921587499998</v>
+        <v>47.67055574999998</v>
       </c>
       <c r="Q35">
-        <v>91.46921587499997</v>
+        <v>90.57055574999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1036925305225441</v>
+        <v>0.1044095546806138</v>
       </c>
       <c r="T35">
-        <v>1.128433175194781</v>
+        <v>1.142409310631922</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.637765357013637</v>
+        <v>2.560184022983824</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08724480608920508</v>
+        <v>0.08824411672830561</v>
       </c>
       <c r="C36">
-        <v>1034.762047836614</v>
+        <v>991.5308389872109</v>
       </c>
       <c r="D36">
-        <v>1497.772047836614</v>
+        <v>1471.205838987211</v>
       </c>
       <c r="E36">
-        <v>166.51</v>
+        <v>183.1750000000001</v>
       </c>
       <c r="F36">
-        <v>566.61</v>
+        <v>583.2750000000001</v>
       </c>
       <c r="G36">
         <v>103.6</v>
@@ -4245,45 +4245,45 @@
         <v>104.3</v>
       </c>
       <c r="M36">
-        <v>40.739259</v>
+        <v>44.21224500000001</v>
       </c>
       <c r="N36">
-        <v>63.56074099999998</v>
+        <v>60.08775499999997</v>
       </c>
       <c r="O36">
-        <v>15.89018524999999</v>
+        <v>15.02193874999999</v>
       </c>
       <c r="P36">
-        <v>47.67055574999998</v>
+        <v>45.06581624999998</v>
       </c>
       <c r="Q36">
-        <v>90.57055574999998</v>
+        <v>87.96581624999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1044095546806138</v>
+        <v>0.1051486411204702</v>
       </c>
       <c r="T36">
-        <v>1.142409310631922</v>
+        <v>1.156815481005591</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.560184022983824</v>
+        <v>2.359074957627688</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08824411672830561</v>
+        <v>0.08824892736740614</v>
       </c>
       <c r="C37">
-        <v>991.5308389872109</v>
+        <v>974.7402294875205</v>
       </c>
       <c r="D37">
-        <v>1471.205838987211</v>
+        <v>1471.080229487521</v>
       </c>
       <c r="E37">
-        <v>183.1750000000001</v>
+        <v>199.84</v>
       </c>
       <c r="F37">
-        <v>583.2750000000001</v>
+        <v>599.9400000000001</v>
       </c>
       <c r="G37">
         <v>103.6</v>
@@ -4327,28 +4327,28 @@
         <v>104.3</v>
       </c>
       <c r="M37">
-        <v>44.21224500000001</v>
+        <v>45.47545200000001</v>
       </c>
       <c r="N37">
-        <v>60.08775499999997</v>
+        <v>58.82454799999997</v>
       </c>
       <c r="O37">
-        <v>15.02193874999999</v>
+        <v>14.70613699999999</v>
       </c>
       <c r="P37">
-        <v>45.06581624999998</v>
+        <v>44.11841099999998</v>
       </c>
       <c r="Q37">
-        <v>87.96581624999999</v>
+        <v>87.01841099999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1051486411204702</v>
+        <v>0.1059108240115721</v>
       </c>
       <c r="T37">
-        <v>1.156815481005591</v>
+        <v>1.171671844203437</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.359074957627688</v>
+        <v>2.293545097693586</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08824892736740615</v>
+        <v>0.08825373800650668</v>
       </c>
       <c r="C38">
-        <v>974.7402294875204</v>
+        <v>957.9496414347261</v>
       </c>
       <c r="D38">
-        <v>1471.08022948752</v>
+        <v>1470.954641434726</v>
       </c>
       <c r="E38">
-        <v>199.8399999999999</v>
+        <v>216.505</v>
       </c>
       <c r="F38">
-        <v>599.9399999999999</v>
+        <v>616.605</v>
       </c>
       <c r="G38">
         <v>103.6</v>
@@ -4409,28 +4409,28 @@
         <v>104.3</v>
       </c>
       <c r="M38">
-        <v>45.475452</v>
+        <v>46.73865900000001</v>
       </c>
       <c r="N38">
-        <v>58.82454799999999</v>
+        <v>57.56134099999998</v>
       </c>
       <c r="O38">
-        <v>14.706137</v>
+        <v>14.39033524999999</v>
       </c>
       <c r="P38">
-        <v>44.11841099999999</v>
+        <v>43.17100574999998</v>
       </c>
       <c r="Q38">
-        <v>87.01841099999999</v>
+        <v>86.07100574999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1059108240115721</v>
+        <v>0.1066972031849313</v>
       </c>
       <c r="T38">
-        <v>1.171671844203437</v>
+        <v>1.186999837978992</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.293545097693586</v>
+        <v>2.231557392350516</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08825373800650668</v>
+        <v>0.08825854864560723</v>
       </c>
       <c r="C39">
-        <v>957.9496414347261</v>
+        <v>941.1590748233355</v>
       </c>
       <c r="D39">
-        <v>1470.954641434726</v>
+        <v>1470.829074823336</v>
       </c>
       <c r="E39">
-        <v>216.505</v>
+        <v>233.17</v>
       </c>
       <c r="F39">
-        <v>616.605</v>
+        <v>633.27</v>
       </c>
       <c r="G39">
         <v>103.6</v>
@@ -4491,28 +4491,28 @@
         <v>104.3</v>
       </c>
       <c r="M39">
-        <v>46.73865900000001</v>
+        <v>48.001866</v>
       </c>
       <c r="N39">
-        <v>57.56134099999998</v>
+        <v>56.29813399999998</v>
       </c>
       <c r="O39">
-        <v>14.39033524999999</v>
+        <v>14.0745335</v>
       </c>
       <c r="P39">
-        <v>43.17100574999998</v>
+        <v>42.22360049999999</v>
       </c>
       <c r="Q39">
-        <v>86.07100574999998</v>
+        <v>85.12360049999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1066972031849313</v>
+        <v>0.1075089494283988</v>
       </c>
       <c r="T39">
-        <v>1.186999837978992</v>
+        <v>1.202822283166662</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.231557392350516</v>
+        <v>2.172832197814976</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08825854864560723</v>
+        <v>0.08826335928470774</v>
       </c>
       <c r="C40">
-        <v>941.1590748233355</v>
+        <v>924.3685296478585</v>
       </c>
       <c r="D40">
-        <v>1470.829074823336</v>
+        <v>1470.703529647859</v>
       </c>
       <c r="E40">
-        <v>233.17</v>
+        <v>249.835</v>
       </c>
       <c r="F40">
-        <v>633.27</v>
+        <v>649.9350000000001</v>
       </c>
       <c r="G40">
         <v>103.6</v>
@@ -4573,28 +4573,28 @@
         <v>104.3</v>
       </c>
       <c r="M40">
-        <v>48.001866</v>
+        <v>49.26507300000001</v>
       </c>
       <c r="N40">
-        <v>56.29813399999998</v>
+        <v>55.03492699999997</v>
       </c>
       <c r="O40">
-        <v>14.0745335</v>
+        <v>13.75873174999999</v>
       </c>
       <c r="P40">
-        <v>42.22360049999999</v>
+        <v>41.27619524999998</v>
       </c>
       <c r="Q40">
-        <v>85.12360049999998</v>
+        <v>84.17619524999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1075089494283988</v>
+        <v>0.1083473103027996</v>
       </c>
       <c r="T40">
-        <v>1.202822283166662</v>
+        <v>1.219163497049009</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.172832197814976</v>
+        <v>2.117118551717156</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08826335928470774</v>
+        <v>0.08826816992380829</v>
       </c>
       <c r="C41">
-        <v>924.3685296478585</v>
+        <v>907.5780059028058</v>
       </c>
       <c r="D41">
-        <v>1470.703529647859</v>
+        <v>1470.578005902806</v>
       </c>
       <c r="E41">
-        <v>249.835</v>
+        <v>266.5</v>
       </c>
       <c r="F41">
-        <v>649.9350000000001</v>
+        <v>666.6</v>
       </c>
       <c r="G41">
         <v>103.6</v>
@@ -4655,28 +4655,28 @@
         <v>104.3</v>
       </c>
       <c r="M41">
-        <v>49.26507300000001</v>
+        <v>50.52828000000001</v>
       </c>
       <c r="N41">
-        <v>55.03492699999997</v>
+        <v>53.77171999999997</v>
       </c>
       <c r="O41">
-        <v>13.75873174999999</v>
+        <v>13.44292999999999</v>
       </c>
       <c r="P41">
-        <v>41.27619524999998</v>
+        <v>40.32878999999998</v>
       </c>
       <c r="Q41">
-        <v>84.17619524999998</v>
+        <v>83.22878999999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1083473103027996</v>
+        <v>0.1092136165396805</v>
       </c>
       <c r="T41">
-        <v>1.219163497049009</v>
+        <v>1.236049418060768</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.117118551717156</v>
+        <v>2.064190587924227</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08826816992380829</v>
+        <v>0.0882729805629088</v>
       </c>
       <c r="C42">
-        <v>907.5780059028058</v>
+        <v>890.7875035826914</v>
       </c>
       <c r="D42">
-        <v>1470.578005902806</v>
+        <v>1470.452503582692</v>
       </c>
       <c r="E42">
-        <v>266.5</v>
+        <v>283.1650000000001</v>
       </c>
       <c r="F42">
-        <v>666.6</v>
+        <v>683.2650000000001</v>
       </c>
       <c r="G42">
         <v>103.6</v>
@@ -4737,28 +4737,28 @@
         <v>104.3</v>
       </c>
       <c r="M42">
-        <v>50.52828000000001</v>
+        <v>51.79148700000001</v>
       </c>
       <c r="N42">
-        <v>53.77171999999997</v>
+        <v>52.50851299999997</v>
       </c>
       <c r="O42">
-        <v>13.44292999999999</v>
+        <v>13.12712824999999</v>
       </c>
       <c r="P42">
-        <v>40.32878999999998</v>
+        <v>39.38138474999998</v>
       </c>
       <c r="Q42">
-        <v>83.22878999999998</v>
+        <v>82.28138474999997</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1092136165396805</v>
+        <v>0.110109289089676</v>
       </c>
       <c r="T42">
-        <v>1.236049418060768</v>
+        <v>1.253507743174621</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.064190587924227</v>
+        <v>2.013844476023636</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0882729805629088</v>
+        <v>0.09275079120200934</v>
       </c>
       <c r="C43">
-        <v>890.7875035826914</v>
+        <v>765.9093493322857</v>
       </c>
       <c r="D43">
-        <v>1470.452503582692</v>
+        <v>1362.239349332286</v>
       </c>
       <c r="E43">
-        <v>283.1650000000001</v>
+        <v>299.83</v>
       </c>
       <c r="F43">
-        <v>683.2650000000001</v>
+        <v>699.9300000000001</v>
       </c>
       <c r="G43">
         <v>103.6</v>
@@ -4819,45 +4819,45 @@
         <v>104.3</v>
       </c>
       <c r="M43">
-        <v>51.79148700000001</v>
+        <v>62.9937</v>
       </c>
       <c r="N43">
-        <v>52.50851299999997</v>
+        <v>41.30629999999998</v>
       </c>
       <c r="O43">
-        <v>13.12712824999999</v>
+        <v>10.32657499999999</v>
       </c>
       <c r="P43">
-        <v>39.38138474999998</v>
+        <v>30.97972499999998</v>
       </c>
       <c r="Q43">
-        <v>82.28138474999997</v>
+        <v>73.87972499999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.110109289089676</v>
+        <v>0.1110358469000161</v>
       </c>
       <c r="T43">
-        <v>1.253507743174621</v>
+        <v>1.271568079499296</v>
       </c>
       <c r="U43">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.013844476023636</v>
+        <v>1.655721127668322</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09275079120200935</v>
+        <v>0.09286210184110988</v>
       </c>
       <c r="C44">
-        <v>765.9093493322856</v>
+        <v>746.7568689063005</v>
       </c>
       <c r="D44">
-        <v>1362.239349332286</v>
+        <v>1359.751868906301</v>
       </c>
       <c r="E44">
-        <v>299.8299999999999</v>
+        <v>316.495</v>
       </c>
       <c r="F44">
-        <v>699.9299999999999</v>
+        <v>716.595</v>
       </c>
       <c r="G44">
         <v>103.6</v>
@@ -4901,28 +4901,28 @@
         <v>104.3</v>
       </c>
       <c r="M44">
-        <v>62.99369999999999</v>
+        <v>64.49355</v>
       </c>
       <c r="N44">
-        <v>41.30629999999999</v>
+        <v>39.80644999999998</v>
       </c>
       <c r="O44">
-        <v>10.326575</v>
+        <v>9.951612499999996</v>
       </c>
       <c r="P44">
-        <v>30.97972499999999</v>
+        <v>29.85483749999999</v>
       </c>
       <c r="Q44">
-        <v>73.87972499999999</v>
+        <v>72.75483749999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1110358469000161</v>
+        <v>0.1119949155107191</v>
       </c>
       <c r="T44">
-        <v>1.271568079499296</v>
+        <v>1.290262111835363</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.655721127668322</v>
+        <v>1.617215985164408</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09286210184110988</v>
+        <v>0.09297341248021043</v>
       </c>
       <c r="C45">
-        <v>746.7568689063005</v>
+        <v>727.6134563153344</v>
       </c>
       <c r="D45">
-        <v>1359.751868906301</v>
+        <v>1357.273456315334</v>
       </c>
       <c r="E45">
-        <v>316.495</v>
+        <v>333.16</v>
       </c>
       <c r="F45">
-        <v>716.595</v>
+        <v>733.26</v>
       </c>
       <c r="G45">
         <v>103.6</v>
@@ -4983,28 +4983,28 @@
         <v>104.3</v>
       </c>
       <c r="M45">
-        <v>64.49355</v>
+        <v>65.99339999999999</v>
       </c>
       <c r="N45">
-        <v>39.80644999999998</v>
+        <v>38.30659999999999</v>
       </c>
       <c r="O45">
-        <v>9.951612499999996</v>
+        <v>9.576649999999997</v>
       </c>
       <c r="P45">
-        <v>29.85483749999999</v>
+        <v>28.72994999999999</v>
       </c>
       <c r="Q45">
-        <v>72.75483749999998</v>
+        <v>71.62994999999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1119949155107191</v>
+        <v>0.1129882365718043</v>
       </c>
       <c r="T45">
-        <v>1.290262111835363</v>
+        <v>1.309623788183433</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.617215985164408</v>
+        <v>1.580461076410671</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09297341248021043</v>
+        <v>0.09308472311931096</v>
       </c>
       <c r="C46">
-        <v>727.6134563153344</v>
+        <v>708.4790620659145</v>
       </c>
       <c r="D46">
-        <v>1357.273456315334</v>
+        <v>1354.804062065915</v>
       </c>
       <c r="E46">
-        <v>333.16</v>
+        <v>349.825</v>
       </c>
       <c r="F46">
-        <v>733.26</v>
+        <v>749.9250000000001</v>
       </c>
       <c r="G46">
         <v>103.6</v>
@@ -5065,28 +5065,28 @@
         <v>104.3</v>
       </c>
       <c r="M46">
-        <v>65.99339999999999</v>
+        <v>67.49325</v>
       </c>
       <c r="N46">
-        <v>38.30659999999999</v>
+        <v>36.80674999999998</v>
       </c>
       <c r="O46">
-        <v>9.576649999999997</v>
+        <v>9.201687499999995</v>
       </c>
       <c r="P46">
-        <v>28.72994999999999</v>
+        <v>27.60506249999998</v>
       </c>
       <c r="Q46">
-        <v>71.62994999999999</v>
+        <v>70.50506249999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1129882365718043</v>
+        <v>0.1140176783987472</v>
       </c>
       <c r="T46">
-        <v>1.309623788183433</v>
+        <v>1.329689525489614</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.580461076410671</v>
+        <v>1.545339719157101</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09308472311931096</v>
+        <v>0.0931960337584115</v>
       </c>
       <c r="C47">
-        <v>708.4790620659145</v>
+        <v>689.3536370241007</v>
       </c>
       <c r="D47">
-        <v>1354.804062065915</v>
+        <v>1352.343637024101</v>
       </c>
       <c r="E47">
-        <v>349.825</v>
+        <v>366.49</v>
       </c>
       <c r="F47">
-        <v>749.9250000000001</v>
+        <v>766.59</v>
       </c>
       <c r="G47">
         <v>103.6</v>
@@ -5147,28 +5147,28 @@
         <v>104.3</v>
       </c>
       <c r="M47">
-        <v>67.49325</v>
+        <v>68.9931</v>
       </c>
       <c r="N47">
-        <v>36.80674999999998</v>
+        <v>35.30689999999998</v>
       </c>
       <c r="O47">
-        <v>9.201687499999995</v>
+        <v>8.826724999999996</v>
       </c>
       <c r="P47">
-        <v>27.60506249999998</v>
+        <v>26.48017499999999</v>
       </c>
       <c r="Q47">
-        <v>70.50506249999998</v>
+        <v>69.38017499999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1140176783987472</v>
+        <v>0.115085247700762</v>
       </c>
       <c r="T47">
-        <v>1.329689525489614</v>
+        <v>1.35049843825158</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.545339719157101</v>
+        <v>1.511745377436294</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0931960337584115</v>
+        <v>0.115393252131621</v>
       </c>
       <c r="C48">
-        <v>689.3536370241007</v>
+        <v>313.1415430069775</v>
       </c>
       <c r="D48">
-        <v>1352.343637024101</v>
+        <v>992.7965430069775</v>
       </c>
       <c r="E48">
-        <v>366.49</v>
+        <v>383.155</v>
       </c>
       <c r="F48">
-        <v>766.59</v>
+        <v>783.255</v>
       </c>
       <c r="G48">
         <v>103.6</v>
@@ -5229,45 +5229,45 @@
         <v>104.3</v>
       </c>
       <c r="M48">
-        <v>68.9931</v>
+        <v>114.981834</v>
       </c>
       <c r="N48">
-        <v>35.30689999999998</v>
+        <v>-10.68183400000002</v>
       </c>
       <c r="O48">
-        <v>8.826724999999996</v>
+        <v>-2.670458500000006</v>
       </c>
       <c r="P48">
-        <v>26.48017499999999</v>
+        <v>-8.011375500000018</v>
       </c>
       <c r="Q48">
-        <v>69.38017499999998</v>
+        <v>34.88862449999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.115085247700762</v>
+        <v>0.1170638052605407</v>
       </c>
       <c r="T48">
-        <v>1.35049843825158</v>
+        <v>1.389064207778917</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.25</v>
+        <v>0.2267749529895305</v>
       </c>
       <c r="W48">
-        <v>0.0675</v>
+        <v>0.1135094369011369</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.511745377436294</v>
+        <v>0.9070998119581218</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.115393252131621</v>
+        <v>0.116403252131621</v>
       </c>
       <c r="C49">
-        <v>313.1415430069775</v>
+        <v>284.609855846815</v>
       </c>
       <c r="D49">
-        <v>992.7965430069775</v>
+        <v>980.929855846815</v>
       </c>
       <c r="E49">
-        <v>383.155</v>
+        <v>399.8200000000001</v>
       </c>
       <c r="F49">
-        <v>783.255</v>
+        <v>799.9200000000001</v>
       </c>
       <c r="G49">
         <v>103.6</v>
@@ -5311,37 +5311,37 @@
         <v>104.3</v>
       </c>
       <c r="M49">
-        <v>114.981834</v>
+        <v>117.428256</v>
       </c>
       <c r="N49">
-        <v>-10.68183400000002</v>
+        <v>-13.12825600000004</v>
       </c>
       <c r="O49">
-        <v>-2.670458500000006</v>
+        <v>-3.282064000000009</v>
       </c>
       <c r="P49">
-        <v>-8.011375500000018</v>
+        <v>-9.846192000000027</v>
       </c>
       <c r="Q49">
-        <v>34.88862449999998</v>
+        <v>33.05380799999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1170638052605407</v>
+        <v>0.1184342630540127</v>
       </c>
       <c r="T49">
-        <v>1.389064207778917</v>
+        <v>1.415776981005434</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2267749529895305</v>
+        <v>0.2220504748022485</v>
       </c>
       <c r="W49">
-        <v>0.1135094369011369</v>
+        <v>0.1142029902990299</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9070998119581218</v>
+        <v>0.8882018992089942</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1164032521316209</v>
+        <v>0.1174132521316209</v>
       </c>
       <c r="C50">
-        <v>284.6098558468153</v>
+        <v>256.3584979749735</v>
       </c>
       <c r="D50">
-        <v>980.9298558468154</v>
+        <v>969.3434979749735</v>
       </c>
       <c r="E50">
-        <v>399.8199999999999</v>
+        <v>416.485</v>
       </c>
       <c r="F50">
-        <v>799.92</v>
+        <v>816.585</v>
       </c>
       <c r="G50">
         <v>103.6</v>
@@ -5393,37 +5393,37 @@
         <v>104.3</v>
       </c>
       <c r="M50">
-        <v>117.428256</v>
+        <v>119.874678</v>
       </c>
       <c r="N50">
-        <v>-13.12825600000002</v>
+        <v>-15.57467800000003</v>
       </c>
       <c r="O50">
-        <v>-3.282064000000005</v>
+        <v>-3.893669500000009</v>
       </c>
       <c r="P50">
-        <v>-9.846192000000016</v>
+        <v>-11.68100850000003</v>
       </c>
       <c r="Q50">
-        <v>33.05380799999998</v>
+        <v>31.21899149999997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1184342630540126</v>
+        <v>0.1198584642903658</v>
       </c>
       <c r="T50">
-        <v>1.415776981005434</v>
+        <v>1.443537313966325</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2220504748022486</v>
+        <v>0.2175188324593455</v>
       </c>
       <c r="W50">
-        <v>0.1142029902990299</v>
+        <v>0.1148682353949681</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8882018992089943</v>
+        <v>0.870075329837382</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1174132521316209</v>
+        <v>0.1184232521316209</v>
       </c>
       <c r="C51">
-        <v>256.3584979749735</v>
+        <v>228.3776519333242</v>
       </c>
       <c r="D51">
-        <v>969.3434979749735</v>
+        <v>958.0276519333241</v>
       </c>
       <c r="E51">
-        <v>416.485</v>
+        <v>433.15</v>
       </c>
       <c r="F51">
-        <v>816.585</v>
+        <v>833.25</v>
       </c>
       <c r="G51">
         <v>103.6</v>
@@ -5475,37 +5475,37 @@
         <v>104.3</v>
       </c>
       <c r="M51">
-        <v>119.874678</v>
+        <v>122.3211</v>
       </c>
       <c r="N51">
-        <v>-15.57467800000003</v>
+        <v>-18.02110000000003</v>
       </c>
       <c r="O51">
-        <v>-3.893669500000009</v>
+        <v>-4.505275000000008</v>
       </c>
       <c r="P51">
-        <v>-11.68100850000003</v>
+        <v>-13.51582500000002</v>
       </c>
       <c r="Q51">
-        <v>31.21899149999997</v>
+        <v>29.38417499999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1198584642903658</v>
+        <v>0.1213396335761732</v>
       </c>
       <c r="T51">
-        <v>1.443537313966325</v>
+        <v>1.472408060245652</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2175188324593455</v>
+        <v>0.2131684558101586</v>
       </c>
       <c r="W51">
-        <v>0.1148682353949681</v>
+        <v>0.1155068706870687</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.870075329837382</v>
+        <v>0.8526738232406345</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1184232521316209</v>
+        <v>0.1194332521316209</v>
       </c>
       <c r="C52">
-        <v>228.3776519333242</v>
+        <v>200.6579533990521</v>
       </c>
       <c r="D52">
-        <v>958.0276519333241</v>
+        <v>946.9729533990521</v>
       </c>
       <c r="E52">
-        <v>433.15</v>
+        <v>449.8149999999999</v>
       </c>
       <c r="F52">
-        <v>833.25</v>
+        <v>849.915</v>
       </c>
       <c r="G52">
         <v>103.6</v>
@@ -5557,37 +5557,37 @@
         <v>104.3</v>
       </c>
       <c r="M52">
-        <v>122.3211</v>
+        <v>124.767522</v>
       </c>
       <c r="N52">
-        <v>-18.02110000000003</v>
+        <v>-20.46752200000002</v>
       </c>
       <c r="O52">
-        <v>-4.505275000000008</v>
+        <v>-5.116880500000004</v>
       </c>
       <c r="P52">
-        <v>-13.51582500000002</v>
+        <v>-15.35064150000001</v>
       </c>
       <c r="Q52">
-        <v>29.38417499999997</v>
+        <v>27.54935849999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1213396335761732</v>
+        <v>0.1228812587511971</v>
       </c>
       <c r="T52">
-        <v>1.472408060245652</v>
+        <v>1.502457204332298</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2131684558101586</v>
+        <v>0.2089886821668222</v>
       </c>
       <c r="W52">
-        <v>0.1155068706870687</v>
+        <v>0.1161204614579105</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8526738232406345</v>
+        <v>0.8359547286672888</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1194332521316209</v>
+        <v>0.1204432521316209</v>
       </c>
       <c r="C53">
-        <v>200.6579533990521</v>
+        <v>173.1904653392045</v>
       </c>
       <c r="D53">
-        <v>946.9729533990521</v>
+        <v>936.1704653392045</v>
       </c>
       <c r="E53">
-        <v>449.8149999999999</v>
+        <v>466.48</v>
       </c>
       <c r="F53">
-        <v>849.915</v>
+        <v>866.58</v>
       </c>
       <c r="G53">
         <v>103.6</v>
@@ -5639,37 +5639,37 @@
         <v>104.3</v>
       </c>
       <c r="M53">
-        <v>124.767522</v>
+        <v>127.213944</v>
       </c>
       <c r="N53">
-        <v>-20.46752200000002</v>
+        <v>-22.91394400000003</v>
       </c>
       <c r="O53">
-        <v>-5.116880500000004</v>
+        <v>-5.728486000000007</v>
       </c>
       <c r="P53">
-        <v>-15.35064150000001</v>
+        <v>-17.18545800000002</v>
       </c>
       <c r="Q53">
-        <v>27.54935849999999</v>
+        <v>25.71454199999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1228812587511971</v>
+        <v>0.1244871183085137</v>
       </c>
       <c r="T53">
-        <v>1.502457204332298</v>
+        <v>1.533758396089221</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2089886821668222</v>
+        <v>0.2049696690482294</v>
       </c>
       <c r="W53">
-        <v>0.1161204614579105</v>
+        <v>0.1167104525837199</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8359547286672888</v>
+        <v>0.8198786761929178</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1204432521316209</v>
+        <v>0.1214532521316209</v>
       </c>
       <c r="C54">
-        <v>173.1904653392045</v>
+        <v>145.9666539142585</v>
       </c>
       <c r="D54">
-        <v>936.1704653392045</v>
+        <v>925.6116539142585</v>
       </c>
       <c r="E54">
-        <v>466.48</v>
+        <v>483.145</v>
       </c>
       <c r="F54">
-        <v>866.58</v>
+        <v>883.245</v>
       </c>
       <c r="G54">
         <v>103.6</v>
@@ -5721,37 +5721,37 @@
         <v>104.3</v>
       </c>
       <c r="M54">
-        <v>127.213944</v>
+        <v>129.660366</v>
       </c>
       <c r="N54">
-        <v>-22.91394400000003</v>
+        <v>-25.36036600000003</v>
       </c>
       <c r="O54">
-        <v>-5.728486000000007</v>
+        <v>-6.340091500000007</v>
       </c>
       <c r="P54">
-        <v>-17.18545800000002</v>
+        <v>-19.02027450000002</v>
       </c>
       <c r="Q54">
-        <v>25.71454199999998</v>
+        <v>23.87972549999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1244871183085137</v>
+        <v>0.1261613123150778</v>
       </c>
       <c r="T54">
-        <v>1.533758396089221</v>
+        <v>1.566391553452821</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2049696690482294</v>
+        <v>0.2011023168020364</v>
       </c>
       <c r="W54">
-        <v>0.1167104525837199</v>
+        <v>0.1172781798934611</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8198786761929178</v>
+        <v>0.8044092672081458</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1214532521316209</v>
+        <v>0.1528350055622575</v>
       </c>
       <c r="C55">
-        <v>145.9666539142585</v>
+        <v>-110.8960572025247</v>
       </c>
       <c r="D55">
-        <v>925.6116539142585</v>
+        <v>685.4139427974753</v>
       </c>
       <c r="E55">
-        <v>483.145</v>
+        <v>499.8100000000001</v>
       </c>
       <c r="F55">
-        <v>883.245</v>
+        <v>899.9100000000001</v>
       </c>
       <c r="G55">
         <v>103.6</v>
@@ -5803,45 +5803,45 @@
         <v>104.3</v>
       </c>
       <c r="M55">
-        <v>129.660366</v>
+        <v>180.701928</v>
       </c>
       <c r="N55">
-        <v>-25.36036600000003</v>
+        <v>-76.40192800000003</v>
       </c>
       <c r="O55">
-        <v>-6.340091500000007</v>
+        <v>-19.10048200000001</v>
       </c>
       <c r="P55">
-        <v>-19.02027450000002</v>
+        <v>-57.30144600000002</v>
       </c>
       <c r="Q55">
-        <v>23.87972549999998</v>
+        <v>-14.40144600000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1261613123150778</v>
+        <v>0.130542543953746</v>
       </c>
       <c r="T55">
-        <v>1.566391553452821</v>
+        <v>1.651789912872623</v>
       </c>
       <c r="U55">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.2011023168020364</v>
+        <v>0.1442984050507751</v>
       </c>
       <c r="W55">
-        <v>0.1172781798934611</v>
+        <v>0.1718248802658044</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8044092672081458</v>
+        <v>0.5771936202031003</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1528350055622575</v>
+        <v>0.1543850055622575</v>
       </c>
       <c r="C56">
-        <v>-110.8960572025247</v>
+        <v>-136.2349967723757</v>
       </c>
       <c r="D56">
-        <v>685.4139427974753</v>
+        <v>676.7400032276244</v>
       </c>
       <c r="E56">
-        <v>499.8100000000001</v>
+        <v>516.475</v>
       </c>
       <c r="F56">
-        <v>899.9100000000001</v>
+        <v>916.575</v>
       </c>
       <c r="G56">
         <v>103.6</v>
@@ -5885,37 +5885,37 @@
         <v>104.3</v>
       </c>
       <c r="M56">
-        <v>180.701928</v>
+        <v>184.04826</v>
       </c>
       <c r="N56">
-        <v>-76.40192800000003</v>
+        <v>-79.74826000000004</v>
       </c>
       <c r="O56">
-        <v>-19.10048200000001</v>
+        <v>-19.93706500000001</v>
       </c>
       <c r="P56">
-        <v>-57.30144600000002</v>
+        <v>-59.81119500000003</v>
       </c>
       <c r="Q56">
-        <v>-14.40144600000002</v>
+        <v>-16.91119500000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.130542543953746</v>
+        <v>0.1324257115971625</v>
       </c>
       <c r="T56">
-        <v>1.651789912872623</v>
+        <v>1.688496355380904</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1442984050507751</v>
+        <v>0.1416747976862155</v>
       </c>
       <c r="W56">
-        <v>0.1718248802658044</v>
+        <v>0.1723517006246079</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5771936202031003</v>
+        <v>0.5666991907448621</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1543850055622575</v>
+        <v>0.1559350055622575</v>
       </c>
       <c r="C57">
-        <v>-136.2349967723757</v>
+        <v>-161.357141813543</v>
       </c>
       <c r="D57">
-        <v>676.7400032276244</v>
+        <v>668.2828581864571</v>
       </c>
       <c r="E57">
-        <v>516.475</v>
+        <v>533.1400000000001</v>
       </c>
       <c r="F57">
-        <v>916.575</v>
+        <v>933.2400000000001</v>
       </c>
       <c r="G57">
         <v>103.6</v>
@@ -5967,37 +5967,37 @@
         <v>104.3</v>
       </c>
       <c r="M57">
-        <v>184.04826</v>
+        <v>187.394592</v>
       </c>
       <c r="N57">
-        <v>-79.74826000000004</v>
+        <v>-83.09459200000003</v>
       </c>
       <c r="O57">
-        <v>-19.93706500000001</v>
+        <v>-20.77364800000001</v>
       </c>
       <c r="P57">
-        <v>-59.81119500000003</v>
+        <v>-62.32094400000003</v>
       </c>
       <c r="Q57">
-        <v>-16.91119500000003</v>
+        <v>-19.42094400000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1324257115971625</v>
+        <v>0.1343944777698253</v>
       </c>
       <c r="T57">
-        <v>1.688496355380904</v>
+        <v>1.726871272548652</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1416747976862155</v>
+        <v>0.139144890584676</v>
       </c>
       <c r="W57">
-        <v>0.1723517006246079</v>
+        <v>0.1728597059705971</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5666991907448621</v>
+        <v>0.5565795623387039</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1559350055622575</v>
+        <v>0.1574850055622575</v>
       </c>
       <c r="C58">
-        <v>-161.357141813543</v>
+        <v>-186.2705197796339</v>
       </c>
       <c r="D58">
-        <v>668.2828581864571</v>
+        <v>660.0344802203662</v>
       </c>
       <c r="E58">
-        <v>533.1400000000001</v>
+        <v>549.8050000000001</v>
       </c>
       <c r="F58">
-        <v>933.2400000000001</v>
+        <v>949.9050000000001</v>
       </c>
       <c r="G58">
         <v>103.6</v>
@@ -6049,37 +6049,37 @@
         <v>104.3</v>
       </c>
       <c r="M58">
-        <v>187.394592</v>
+        <v>190.740924</v>
       </c>
       <c r="N58">
-        <v>-83.09459200000003</v>
+        <v>-86.44092400000005</v>
       </c>
       <c r="O58">
-        <v>-20.77364800000001</v>
+        <v>-21.61023100000001</v>
       </c>
       <c r="P58">
-        <v>-62.32094400000003</v>
+        <v>-64.83069300000004</v>
       </c>
       <c r="Q58">
-        <v>-19.42094400000003</v>
+        <v>-21.93069300000004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1343944777698253</v>
+        <v>0.1364548144621469</v>
       </c>
       <c r="T58">
-        <v>1.726871272548652</v>
+        <v>1.767031069584667</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.139144890584676</v>
+        <v>0.1367037521533658</v>
       </c>
       <c r="W58">
-        <v>0.1728597059705971</v>
+        <v>0.1733498865676041</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5565795623387039</v>
+        <v>0.5468150086134633</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1574850055622575</v>
+        <v>0.1590350055622575</v>
       </c>
       <c r="C59">
-        <v>-186.2705197796339</v>
+        <v>-210.9827666362187</v>
       </c>
       <c r="D59">
-        <v>660.0344802203662</v>
+        <v>651.9872333637815</v>
       </c>
       <c r="E59">
-        <v>549.8050000000001</v>
+        <v>566.4700000000001</v>
       </c>
       <c r="F59">
-        <v>949.9050000000001</v>
+        <v>966.5700000000002</v>
       </c>
       <c r="G59">
         <v>103.6</v>
@@ -6131,37 +6131,37 @@
         <v>104.3</v>
       </c>
       <c r="M59">
-        <v>190.740924</v>
+        <v>194.087256</v>
       </c>
       <c r="N59">
-        <v>-86.44092400000005</v>
+        <v>-89.78725600000004</v>
       </c>
       <c r="O59">
-        <v>-21.61023100000001</v>
+        <v>-22.44681400000001</v>
       </c>
       <c r="P59">
-        <v>-64.83069300000004</v>
+        <v>-67.34044200000002</v>
       </c>
       <c r="Q59">
-        <v>-21.93069300000004</v>
+        <v>-24.44044200000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1364548144621469</v>
+        <v>0.1386132624255313</v>
       </c>
       <c r="T59">
-        <v>1.767031069584667</v>
+        <v>1.809103237908112</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1367037521533658</v>
+        <v>0.1343467909093423</v>
       </c>
       <c r="W59">
-        <v>0.1733498865676041</v>
+        <v>0.1738231643854041</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5468150086134633</v>
+        <v>0.5373871636373693</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1590350055622575</v>
+        <v>0.1605850055622575</v>
       </c>
       <c r="C60">
-        <v>-210.9827666362181</v>
+        <v>-235.5011504387896</v>
       </c>
       <c r="D60">
-        <v>651.9872333637818</v>
+        <v>644.1338495612102</v>
       </c>
       <c r="E60">
-        <v>566.4699999999999</v>
+        <v>583.1349999999999</v>
       </c>
       <c r="F60">
-        <v>966.5699999999999</v>
+        <v>983.2349999999999</v>
       </c>
       <c r="G60">
         <v>103.6</v>
@@ -6213,37 +6213,37 @@
         <v>104.3</v>
       </c>
       <c r="M60">
-        <v>194.087256</v>
+        <v>197.433588</v>
       </c>
       <c r="N60">
-        <v>-89.78725600000001</v>
+        <v>-93.133588</v>
       </c>
       <c r="O60">
-        <v>-22.446814</v>
+        <v>-23.283397</v>
       </c>
       <c r="P60">
-        <v>-67.34044200000001</v>
+        <v>-69.850191</v>
       </c>
       <c r="Q60">
-        <v>-24.44044200000001</v>
+        <v>-26.950191</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1386132624255313</v>
+        <v>0.1408770005334711</v>
       </c>
       <c r="T60">
-        <v>1.809103237908111</v>
+        <v>1.853227707125382</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1343467909093423</v>
+        <v>0.1320697266566416</v>
       </c>
       <c r="W60">
-        <v>0.1738231643854041</v>
+        <v>0.1742803988873464</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5373871636373693</v>
+        <v>0.5282789066265665</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1605850055622575</v>
+        <v>0.1621350055622575</v>
       </c>
       <c r="C61">
-        <v>-235.5011504387896</v>
+        <v>-259.832593226983</v>
       </c>
       <c r="D61">
-        <v>644.1338495612102</v>
+        <v>636.4674067730169</v>
       </c>
       <c r="E61">
-        <v>583.1349999999999</v>
+        <v>599.8</v>
       </c>
       <c r="F61">
-        <v>983.2349999999999</v>
+        <v>999.9</v>
       </c>
       <c r="G61">
         <v>103.6</v>
@@ -6295,37 +6295,37 @@
         <v>104.3</v>
       </c>
       <c r="M61">
-        <v>197.433588</v>
+        <v>200.77992</v>
       </c>
       <c r="N61">
-        <v>-93.133588</v>
+        <v>-96.47992000000002</v>
       </c>
       <c r="O61">
-        <v>-23.283397</v>
+        <v>-24.11998000000001</v>
       </c>
       <c r="P61">
-        <v>-69.850191</v>
+        <v>-72.35994000000002</v>
       </c>
       <c r="Q61">
-        <v>-26.950191</v>
+        <v>-29.45994000000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1408770005334711</v>
+        <v>0.1432539255468079</v>
       </c>
       <c r="T61">
-        <v>1.853227707125382</v>
+        <v>1.899558399803517</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1320697266566416</v>
+        <v>0.1298685645456976</v>
       </c>
       <c r="W61">
-        <v>0.1742803988873464</v>
+        <v>0.1747223922392239</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5282789066265665</v>
+        <v>0.5194742581827902</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1621350055622575</v>
+        <v>0.1636850055622575</v>
       </c>
       <c r="C62">
-        <v>-259.832593226983</v>
+        <v>-283.9836913736824</v>
       </c>
       <c r="D62">
-        <v>636.4674067730169</v>
+        <v>628.9813086263175</v>
       </c>
       <c r="E62">
-        <v>599.8</v>
+        <v>616.4649999999999</v>
       </c>
       <c r="F62">
-        <v>999.9</v>
+        <v>1016.565</v>
       </c>
       <c r="G62">
         <v>103.6</v>
@@ -6377,37 +6377,37 @@
         <v>104.3</v>
       </c>
       <c r="M62">
-        <v>200.77992</v>
+        <v>204.126252</v>
       </c>
       <c r="N62">
-        <v>-96.47992000000002</v>
+        <v>-99.82625200000001</v>
       </c>
       <c r="O62">
-        <v>-24.11998000000001</v>
+        <v>-24.956563</v>
       </c>
       <c r="P62">
-        <v>-72.35994000000002</v>
+        <v>-74.86968900000001</v>
       </c>
       <c r="Q62">
-        <v>-29.45994000000002</v>
+        <v>-31.96968900000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1432539255468079</v>
+        <v>0.1457527441505722</v>
       </c>
       <c r="T62">
-        <v>1.899558399803517</v>
+        <v>1.948265025439504</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1298685645456976</v>
+        <v>0.1277395716842927</v>
       </c>
       <c r="W62">
-        <v>0.1747223922392239</v>
+        <v>0.175149894005794</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5194742581827902</v>
+        <v>0.5109582867371708</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1636850055622575</v>
+        <v>0.1652350055622575</v>
       </c>
       <c r="C63">
-        <v>-283.9836913736824</v>
+        <v>-307.9607345147524</v>
       </c>
       <c r="D63">
-        <v>628.9813086263175</v>
+        <v>621.6692654852476</v>
       </c>
       <c r="E63">
-        <v>616.4649999999999</v>
+        <v>633.13</v>
       </c>
       <c r="F63">
-        <v>1016.565</v>
+        <v>1033.23</v>
       </c>
       <c r="G63">
         <v>103.6</v>
@@ -6459,37 +6459,37 @@
         <v>104.3</v>
       </c>
       <c r="M63">
-        <v>204.126252</v>
+        <v>207.472584</v>
       </c>
       <c r="N63">
-        <v>-99.82625200000001</v>
+        <v>-103.172584</v>
       </c>
       <c r="O63">
-        <v>-24.956563</v>
+        <v>-25.79314600000001</v>
       </c>
       <c r="P63">
-        <v>-74.86968900000001</v>
+        <v>-77.37943800000002</v>
       </c>
       <c r="Q63">
-        <v>-31.96968900000001</v>
+        <v>-34.47943800000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1457527441505722</v>
+        <v>0.1483830795229556</v>
       </c>
       <c r="T63">
-        <v>1.948265025439504</v>
+        <v>1.999535157687913</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1277395716842927</v>
+        <v>0.1256792560119654</v>
       </c>
       <c r="W63">
-        <v>0.175149894005794</v>
+        <v>0.1755636053927974</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5109582867371708</v>
+        <v>0.5027170240478616</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1652350055622575</v>
+        <v>0.1893239627078777</v>
       </c>
       <c r="C64">
-        <v>-307.9607345147524</v>
+        <v>-419.7558407624018</v>
       </c>
       <c r="D64">
-        <v>621.6692654852476</v>
+        <v>526.5391592375981</v>
       </c>
       <c r="E64">
-        <v>633.13</v>
+        <v>649.795</v>
       </c>
       <c r="F64">
-        <v>1033.23</v>
+        <v>1049.895</v>
       </c>
       <c r="G64">
         <v>103.6</v>
@@ -6541,45 +6541,45 @@
         <v>104.3</v>
       </c>
       <c r="M64">
-        <v>207.472584</v>
+        <v>247.565241</v>
       </c>
       <c r="N64">
-        <v>-103.172584</v>
+        <v>-143.265241</v>
       </c>
       <c r="O64">
-        <v>-25.79314600000001</v>
+        <v>-35.81631025000001</v>
       </c>
       <c r="P64">
-        <v>-77.37943800000002</v>
+        <v>-107.44893075</v>
       </c>
       <c r="Q64">
-        <v>-34.47943800000002</v>
+        <v>-64.54893075000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1483830795229556</v>
+        <v>0.1524771009847116</v>
       </c>
       <c r="T64">
-        <v>1.999535157687913</v>
+        <v>2.079335256175676</v>
       </c>
       <c r="U64">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1256792560119654</v>
+        <v>0.1053257714801731</v>
       </c>
       <c r="W64">
-        <v>0.1755636053927974</v>
+        <v>0.2109641830849752</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5027170240478616</v>
+        <v>0.4213030859206927</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1893239627078777</v>
+        <v>0.1912239627078777</v>
       </c>
       <c r="C65">
-        <v>-419.7558407624018</v>
+        <v>-442.7001875280259</v>
       </c>
       <c r="D65">
-        <v>526.5391592375981</v>
+        <v>520.259812471974</v>
       </c>
       <c r="E65">
-        <v>649.795</v>
+        <v>666.4599999999999</v>
       </c>
       <c r="F65">
-        <v>1049.895</v>
+        <v>1066.56</v>
       </c>
       <c r="G65">
         <v>103.6</v>
@@ -6623,37 +6623,37 @@
         <v>104.3</v>
       </c>
       <c r="M65">
-        <v>247.565241</v>
+        <v>251.494848</v>
       </c>
       <c r="N65">
-        <v>-143.265241</v>
+        <v>-147.194848</v>
       </c>
       <c r="O65">
-        <v>-35.81631025000001</v>
+        <v>-36.798712</v>
       </c>
       <c r="P65">
-        <v>-107.44893075</v>
+        <v>-110.396136</v>
       </c>
       <c r="Q65">
-        <v>-64.54893075000001</v>
+        <v>-67.49613600000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1524771009847116</v>
+        <v>0.1554403537898425</v>
       </c>
       <c r="T65">
-        <v>2.079335256175676</v>
+        <v>2.137094568847223</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1053257714801731</v>
+        <v>0.1036800563007955</v>
       </c>
       <c r="W65">
-        <v>0.2109641830849752</v>
+        <v>0.2113522427242724</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4213030859206927</v>
+        <v>0.4147202252031819</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1912239627078777</v>
+        <v>0.1931239627078777</v>
       </c>
       <c r="C66">
-        <v>-442.7001875280259</v>
+        <v>-465.4965281889123</v>
       </c>
       <c r="D66">
-        <v>520.259812471974</v>
+        <v>514.1284718110878</v>
       </c>
       <c r="E66">
-        <v>666.4599999999999</v>
+        <v>683.1250000000001</v>
       </c>
       <c r="F66">
-        <v>1066.56</v>
+        <v>1083.225</v>
       </c>
       <c r="G66">
         <v>103.6</v>
@@ -6705,37 +6705,37 @@
         <v>104.3</v>
       </c>
       <c r="M66">
-        <v>251.494848</v>
+        <v>255.4244550000001</v>
       </c>
       <c r="N66">
-        <v>-147.194848</v>
+        <v>-151.1244550000001</v>
       </c>
       <c r="O66">
-        <v>-36.798712</v>
+        <v>-37.78111375000002</v>
       </c>
       <c r="P66">
-        <v>-110.396136</v>
+        <v>-113.3433412500001</v>
       </c>
       <c r="Q66">
-        <v>-67.49613600000001</v>
+        <v>-70.44334125000006</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1554403537898425</v>
+        <v>0.1585729353266952</v>
       </c>
       <c r="T66">
-        <v>2.137094568847223</v>
+        <v>2.19815441367143</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1036800563007955</v>
+        <v>0.1020849785115524</v>
       </c>
       <c r="W66">
-        <v>0.2113522427242724</v>
+        <v>0.211728362066976</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4147202252031819</v>
+        <v>0.4083399140462097</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1931239627078777</v>
+        <v>0.1950239627078777</v>
       </c>
       <c r="C67">
-        <v>-465.4965281889123</v>
+        <v>-488.1500346168289</v>
       </c>
       <c r="D67">
-        <v>514.1284718110878</v>
+        <v>508.1399653831712</v>
       </c>
       <c r="E67">
-        <v>683.1250000000001</v>
+        <v>699.7900000000001</v>
       </c>
       <c r="F67">
-        <v>1083.225</v>
+        <v>1099.89</v>
       </c>
       <c r="G67">
         <v>103.6</v>
@@ -6787,37 +6787,37 @@
         <v>104.3</v>
       </c>
       <c r="M67">
-        <v>255.4244550000001</v>
+        <v>259.3540620000001</v>
       </c>
       <c r="N67">
-        <v>-151.1244550000001</v>
+        <v>-155.0540620000001</v>
       </c>
       <c r="O67">
-        <v>-37.78111375000002</v>
+        <v>-38.76351550000002</v>
       </c>
       <c r="P67">
-        <v>-113.3433412500001</v>
+        <v>-116.2905465000001</v>
       </c>
       <c r="Q67">
-        <v>-70.44334125000006</v>
+        <v>-73.39054650000006</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1585729353266952</v>
+        <v>0.1618897863657156</v>
       </c>
       <c r="T67">
-        <v>2.19815441367143</v>
+        <v>2.262806014073531</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1020849785115524</v>
+        <v>0.1005382364128925</v>
       </c>
       <c r="W67">
-        <v>0.211728362066976</v>
+        <v>0.21209308385384</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4083399140462097</v>
+        <v>0.4021529456515702</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1950239627078777</v>
+        <v>0.1969239627078777</v>
       </c>
       <c r="C68">
-        <v>-488.1500346168289</v>
+        <v>-510.6656404926094</v>
       </c>
       <c r="D68">
-        <v>508.1399653831712</v>
+        <v>502.2893595073907</v>
       </c>
       <c r="E68">
-        <v>699.7900000000001</v>
+        <v>716.455</v>
       </c>
       <c r="F68">
-        <v>1099.89</v>
+        <v>1116.555</v>
       </c>
       <c r="G68">
         <v>103.6</v>
@@ -6869,37 +6869,37 @@
         <v>104.3</v>
       </c>
       <c r="M68">
-        <v>259.3540620000001</v>
+        <v>263.283669</v>
       </c>
       <c r="N68">
-        <v>-155.0540620000001</v>
+        <v>-158.983669</v>
       </c>
       <c r="O68">
-        <v>-38.76351550000002</v>
+        <v>-39.74591725000001</v>
       </c>
       <c r="P68">
-        <v>-116.2905465000001</v>
+        <v>-119.23775175</v>
       </c>
       <c r="Q68">
-        <v>-73.39054650000006</v>
+        <v>-76.33775175000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1618897863657156</v>
+        <v>0.1654076586798282</v>
       </c>
       <c r="T68">
-        <v>2.262806014073531</v>
+        <v>2.33137589328788</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1005382364128925</v>
+        <v>0.09903766572016282</v>
       </c>
       <c r="W68">
-        <v>0.21209308385384</v>
+        <v>0.2124469184231856</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4021529456515702</v>
+        <v>0.3961506628806513</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1969239627078777</v>
+        <v>0.1988239627078777</v>
       </c>
       <c r="C69">
-        <v>-510.6656404926094</v>
+        <v>-533.0480548624453</v>
       </c>
       <c r="D69">
-        <v>502.2893595073907</v>
+        <v>496.5719451375547</v>
       </c>
       <c r="E69">
-        <v>716.455</v>
+        <v>733.12</v>
       </c>
       <c r="F69">
-        <v>1116.555</v>
+        <v>1133.22</v>
       </c>
       <c r="G69">
         <v>103.6</v>
@@ -6951,37 +6951,37 @@
         <v>104.3</v>
       </c>
       <c r="M69">
-        <v>263.283669</v>
+        <v>267.213276</v>
       </c>
       <c r="N69">
-        <v>-158.983669</v>
+        <v>-162.913276</v>
       </c>
       <c r="O69">
-        <v>-39.74591725000001</v>
+        <v>-40.72831900000001</v>
       </c>
       <c r="P69">
-        <v>-119.23775175</v>
+        <v>-122.184957</v>
       </c>
       <c r="Q69">
-        <v>-76.33775175000002</v>
+        <v>-79.28495700000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1654076586798282</v>
+        <v>0.1691453980135728</v>
       </c>
       <c r="T69">
-        <v>2.33137589328788</v>
+        <v>2.404231389953126</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09903766572016282</v>
+        <v>0.09758122945957219</v>
       </c>
       <c r="W69">
-        <v>0.2124469184231856</v>
+        <v>0.2127903460934329</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3961506628806513</v>
+        <v>0.3903249178382888</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1988239627078777</v>
+        <v>0.2007239627078777</v>
       </c>
       <c r="C70">
-        <v>-533.0480548624453</v>
+        <v>-555.3017747787529</v>
       </c>
       <c r="D70">
-        <v>496.5719451375547</v>
+        <v>490.9832252212471</v>
       </c>
       <c r="E70">
-        <v>733.12</v>
+        <v>749.785</v>
       </c>
       <c r="F70">
-        <v>1133.22</v>
+        <v>1149.885</v>
       </c>
       <c r="G70">
         <v>103.6</v>
@@ -7033,37 +7033,37 @@
         <v>104.3</v>
       </c>
       <c r="M70">
-        <v>267.213276</v>
+        <v>271.142883</v>
       </c>
       <c r="N70">
-        <v>-162.913276</v>
+        <v>-166.842883</v>
       </c>
       <c r="O70">
-        <v>-40.72831900000001</v>
+        <v>-41.71072075</v>
       </c>
       <c r="P70">
-        <v>-122.184957</v>
+        <v>-125.13216225</v>
       </c>
       <c r="Q70">
-        <v>-79.28495700000002</v>
+        <v>-82.23216224999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1691453980135728</v>
+        <v>0.1731242818204623</v>
       </c>
       <c r="T70">
-        <v>2.404231389953126</v>
+        <v>2.481787241241937</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09758122945957219</v>
+        <v>0.0961670087427668</v>
       </c>
       <c r="W70">
-        <v>0.2127903460934329</v>
+        <v>0.2131238193384556</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3903249178382888</v>
+        <v>0.3846680349710673</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2007239627078777</v>
+        <v>0.2026239627078777</v>
       </c>
       <c r="C71">
-        <v>-555.3017747787529</v>
+        <v>-577.4310970969349</v>
       </c>
       <c r="D71">
-        <v>490.9832252212471</v>
+        <v>485.5189029030653</v>
       </c>
       <c r="E71">
-        <v>749.785</v>
+        <v>766.4500000000002</v>
       </c>
       <c r="F71">
-        <v>1149.885</v>
+        <v>1166.55</v>
       </c>
       <c r="G71">
         <v>103.6</v>
@@ -7115,37 +7115,37 @@
         <v>104.3</v>
       </c>
       <c r="M71">
-        <v>271.142883</v>
+        <v>275.0724900000001</v>
       </c>
       <c r="N71">
-        <v>-166.842883</v>
+        <v>-170.7724900000001</v>
       </c>
       <c r="O71">
-        <v>-41.71072075</v>
+        <v>-42.69312250000002</v>
       </c>
       <c r="P71">
-        <v>-125.13216225</v>
+        <v>-128.0793675000001</v>
       </c>
       <c r="Q71">
-        <v>-82.23216224999999</v>
+        <v>-85.17936750000007</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1731242818204623</v>
+        <v>0.177368424547811</v>
       </c>
       <c r="T71">
-        <v>2.481787241241937</v>
+        <v>2.564513482616668</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0961670087427668</v>
+        <v>0.09479319433215583</v>
       </c>
       <c r="W71">
-        <v>0.2131238193384556</v>
+        <v>0.2134477647764777</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3846680349710673</v>
+        <v>0.3791727773286233</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2026239627078777</v>
+        <v>0.2045239627078777</v>
       </c>
       <c r="C72">
-        <v>-577.4310970969349</v>
+        <v>-599.4401294930698</v>
       </c>
       <c r="D72">
-        <v>485.5189029030653</v>
+        <v>480.1748705069303</v>
       </c>
       <c r="E72">
-        <v>766.4500000000002</v>
+        <v>783.1150000000001</v>
       </c>
       <c r="F72">
-        <v>1166.55</v>
+        <v>1183.215</v>
       </c>
       <c r="G72">
         <v>103.6</v>
@@ -7197,37 +7197,37 @@
         <v>104.3</v>
       </c>
       <c r="M72">
-        <v>275.0724900000001</v>
+        <v>279.002097</v>
       </c>
       <c r="N72">
-        <v>-170.7724900000001</v>
+        <v>-174.7020970000001</v>
       </c>
       <c r="O72">
-        <v>-42.69312250000002</v>
+        <v>-43.67552425000002</v>
       </c>
       <c r="P72">
-        <v>-128.0793675000001</v>
+        <v>-131.02657275</v>
       </c>
       <c r="Q72">
-        <v>-85.17936750000007</v>
+        <v>-88.12657275000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.177368424547811</v>
+        <v>0.1819052667735976</v>
       </c>
       <c r="T72">
-        <v>2.564513482616668</v>
+        <v>2.652944982017243</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09479319433215583</v>
+        <v>0.09345807891902687</v>
       </c>
       <c r="W72">
-        <v>0.2134477647764777</v>
+        <v>0.2137625849908935</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3791727773286233</v>
+        <v>0.3738323156761075</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2045239627078776</v>
+        <v>0.2064239627078777</v>
       </c>
       <c r="C73">
-        <v>-599.4401294930694</v>
+        <v>-621.3328007619029</v>
       </c>
       <c r="D73">
-        <v>480.1748705069305</v>
+        <v>474.947199238097</v>
       </c>
       <c r="E73">
-        <v>783.1149999999999</v>
+        <v>799.7799999999999</v>
       </c>
       <c r="F73">
-        <v>1183.215</v>
+        <v>1199.88</v>
       </c>
       <c r="G73">
         <v>103.6</v>
@@ -7279,37 +7279,37 @@
         <v>104.3</v>
       </c>
       <c r="M73">
-        <v>279.002097</v>
+        <v>282.931704</v>
       </c>
       <c r="N73">
-        <v>-174.702097</v>
+        <v>-178.631704</v>
       </c>
       <c r="O73">
-        <v>-43.67552425</v>
+        <v>-44.657926</v>
       </c>
       <c r="P73">
-        <v>-131.02657275</v>
+        <v>-133.973778</v>
       </c>
       <c r="Q73">
-        <v>-88.12657275000001</v>
+        <v>-91.07377799999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1819052667735976</v>
+        <v>0.1867661691583689</v>
       </c>
       <c r="T73">
-        <v>2.652944982017242</v>
+        <v>2.747693017089287</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0934580789190269</v>
+        <v>0.09216005004515153</v>
       </c>
       <c r="W73">
-        <v>0.2137625849908935</v>
+        <v>0.2140686601993533</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3738323156761075</v>
+        <v>0.3686402001806061</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2064239627078777</v>
+        <v>0.2083239627078777</v>
       </c>
       <c r="C74">
-        <v>-621.3328007619029</v>
+        <v>-643.1128704493975</v>
       </c>
       <c r="D74">
-        <v>474.947199238097</v>
+        <v>469.8321295506026</v>
       </c>
       <c r="E74">
-        <v>799.7799999999999</v>
+        <v>816.4450000000001</v>
       </c>
       <c r="F74">
-        <v>1199.88</v>
+        <v>1216.545</v>
       </c>
       <c r="G74">
         <v>103.6</v>
@@ -7361,37 +7361,37 @@
         <v>104.3</v>
       </c>
       <c r="M74">
-        <v>282.931704</v>
+        <v>286.861311</v>
       </c>
       <c r="N74">
-        <v>-178.631704</v>
+        <v>-182.561311</v>
       </c>
       <c r="O74">
-        <v>-44.657926</v>
+        <v>-45.64032775</v>
       </c>
       <c r="P74">
-        <v>-133.973778</v>
+        <v>-136.92098325</v>
       </c>
       <c r="Q74">
-        <v>-91.07377799999998</v>
+        <v>-94.02098325</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1867661691583689</v>
+        <v>0.1919871383864567</v>
       </c>
       <c r="T74">
-        <v>2.747693017089287</v>
+        <v>2.849459425129631</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09216005004515153</v>
+        <v>0.09089758360617683</v>
       </c>
       <c r="W74">
-        <v>0.2140686601993533</v>
+        <v>0.2143663497856635</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3686402001806061</v>
+        <v>0.3635903344247073</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2083239627078777</v>
+        <v>0.2102239627078777</v>
       </c>
       <c r="C75">
-        <v>-643.1128704493975</v>
+        <v>-664.7839378694716</v>
       </c>
       <c r="D75">
-        <v>469.8321295506026</v>
+        <v>464.8260621305284</v>
       </c>
       <c r="E75">
-        <v>816.4450000000001</v>
+        <v>833.11</v>
       </c>
       <c r="F75">
-        <v>1216.545</v>
+        <v>1233.21</v>
       </c>
       <c r="G75">
         <v>103.6</v>
@@ -7443,37 +7443,37 @@
         <v>104.3</v>
       </c>
       <c r="M75">
-        <v>286.861311</v>
+        <v>290.790918</v>
       </c>
       <c r="N75">
-        <v>-182.561311</v>
+        <v>-186.4909180000001</v>
       </c>
       <c r="O75">
-        <v>-45.64032775</v>
+        <v>-46.62272950000001</v>
       </c>
       <c r="P75">
-        <v>-136.92098325</v>
+        <v>-139.8681885</v>
       </c>
       <c r="Q75">
-        <v>-94.02098325</v>
+        <v>-96.96818850000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1919871383864567</v>
+        <v>0.1976097206320896</v>
       </c>
       <c r="T75">
-        <v>2.849459425129631</v>
+        <v>2.959054018403847</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09089758360617683</v>
+        <v>0.08966923788176903</v>
       </c>
       <c r="W75">
-        <v>0.2143663497856635</v>
+        <v>0.2146559937074789</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3635903344247073</v>
+        <v>0.3586769515270761</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2102239627078777</v>
+        <v>0.2121239627078776</v>
       </c>
       <c r="C76">
-        <v>-664.7839378694716</v>
+        <v>-686.3494505503767</v>
       </c>
       <c r="D76">
-        <v>464.8260621305284</v>
+        <v>459.9255494496234</v>
       </c>
       <c r="E76">
-        <v>833.11</v>
+        <v>849.775</v>
       </c>
       <c r="F76">
-        <v>1233.21</v>
+        <v>1249.875</v>
       </c>
       <c r="G76">
         <v>103.6</v>
@@ -7525,37 +7525,37 @@
         <v>104.3</v>
       </c>
       <c r="M76">
-        <v>290.790918</v>
+        <v>294.720525</v>
       </c>
       <c r="N76">
-        <v>-186.4909180000001</v>
+        <v>-190.420525</v>
       </c>
       <c r="O76">
-        <v>-46.62272950000001</v>
+        <v>-47.60513125000001</v>
       </c>
       <c r="P76">
-        <v>-139.8681885</v>
+        <v>-142.81539375</v>
       </c>
       <c r="Q76">
-        <v>-96.96818850000002</v>
+        <v>-99.91539375000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1976097206320896</v>
+        <v>0.2036821094573732</v>
       </c>
       <c r="T76">
-        <v>2.959054018403847</v>
+        <v>3.077416179140001</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08966923788176903</v>
+        <v>0.08847364804334545</v>
       </c>
       <c r="W76">
-        <v>0.2146559937074789</v>
+        <v>0.2149379137913791</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3586769515270761</v>
+        <v>0.3538945921733818</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2121239627078776</v>
+        <v>0.2140239627078777</v>
       </c>
       <c r="C77">
-        <v>-686.3494505503767</v>
+        <v>-707.8127121523626</v>
       </c>
       <c r="D77">
-        <v>459.9255494496234</v>
+        <v>455.1272878476374</v>
       </c>
       <c r="E77">
-        <v>849.775</v>
+        <v>866.4399999999999</v>
       </c>
       <c r="F77">
-        <v>1249.875</v>
+        <v>1266.54</v>
       </c>
       <c r="G77">
         <v>103.6</v>
@@ -7607,37 +7607,37 @@
         <v>104.3</v>
       </c>
       <c r="M77">
-        <v>294.720525</v>
+        <v>298.650132</v>
       </c>
       <c r="N77">
-        <v>-190.420525</v>
+        <v>-194.350132</v>
       </c>
       <c r="O77">
-        <v>-47.60513125000001</v>
+        <v>-48.587533</v>
       </c>
       <c r="P77">
-        <v>-142.81539375</v>
+        <v>-145.762599</v>
       </c>
       <c r="Q77">
-        <v>-99.91539375000002</v>
+        <v>-102.862599</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2036821094573732</v>
+        <v>0.2102605306847638</v>
       </c>
       <c r="T77">
-        <v>3.077416179140001</v>
+        <v>3.205641853270835</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08847364804334545</v>
+        <v>0.08730952109540671</v>
       </c>
       <c r="W77">
-        <v>0.2149379137913791</v>
+        <v>0.2152124149257031</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3538945921733818</v>
+        <v>0.3492380843816268</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2140239627078777</v>
+        <v>0.2159239627078777</v>
       </c>
       <c r="C78">
-        <v>-707.8127121523626</v>
+        <v>-729.1768898948453</v>
       </c>
       <c r="D78">
-        <v>455.1272878476374</v>
+        <v>450.4281101051546</v>
       </c>
       <c r="E78">
-        <v>866.4399999999999</v>
+        <v>883.1049999999999</v>
       </c>
       <c r="F78">
-        <v>1266.54</v>
+        <v>1283.205</v>
       </c>
       <c r="G78">
         <v>103.6</v>
@@ -7689,37 +7689,37 @@
         <v>104.3</v>
       </c>
       <c r="M78">
-        <v>298.650132</v>
+        <v>302.579739</v>
       </c>
       <c r="N78">
-        <v>-194.350132</v>
+        <v>-198.279739</v>
       </c>
       <c r="O78">
-        <v>-48.587533</v>
+        <v>-49.56993475000001</v>
       </c>
       <c r="P78">
-        <v>-145.762599</v>
+        <v>-148.70980425</v>
       </c>
       <c r="Q78">
-        <v>-102.862599</v>
+        <v>-105.80980425</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2102605306847638</v>
+        <v>0.2174109885406231</v>
       </c>
       <c r="T78">
-        <v>3.205641853270835</v>
+        <v>3.345017586021741</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08730952109540671</v>
+        <v>0.08617563121105076</v>
       </c>
       <c r="W78">
-        <v>0.2152124149257031</v>
+        <v>0.2154797861604342</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3492380843816268</v>
+        <v>0.3447025248442031</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2159239627078777</v>
+        <v>0.2178239627078777</v>
       </c>
       <c r="C79">
-        <v>-729.1768898948453</v>
+        <v>-750.4450215281634</v>
       </c>
       <c r="D79">
-        <v>450.4281101051546</v>
+        <v>445.8249784718367</v>
       </c>
       <c r="E79">
-        <v>883.1049999999999</v>
+        <v>899.7700000000001</v>
       </c>
       <c r="F79">
-        <v>1283.205</v>
+        <v>1299.87</v>
       </c>
       <c r="G79">
         <v>103.6</v>
@@ -7771,37 +7771,37 @@
         <v>104.3</v>
       </c>
       <c r="M79">
-        <v>302.579739</v>
+        <v>306.5093460000001</v>
       </c>
       <c r="N79">
-        <v>-198.279739</v>
+        <v>-202.2093460000001</v>
       </c>
       <c r="O79">
-        <v>-49.56993475000001</v>
+        <v>-50.55233650000002</v>
       </c>
       <c r="P79">
-        <v>-148.70980425</v>
+        <v>-151.6570095</v>
       </c>
       <c r="Q79">
-        <v>-105.80980425</v>
+        <v>-108.7570095</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2174109885406231</v>
+        <v>0.2252114880197423</v>
       </c>
       <c r="T79">
-        <v>3.345017586021741</v>
+        <v>3.497063839931819</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08617563121105076</v>
+        <v>0.08507081542629369</v>
       </c>
       <c r="W79">
-        <v>0.2154797861604342</v>
+        <v>0.21574030172248</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3447025248442031</v>
+        <v>0.3402832617051748</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2178239627078777</v>
+        <v>0.2197239627078777</v>
       </c>
       <c r="C80">
-        <v>-750.4450215281634</v>
+        <v>-771.6200218821749</v>
       </c>
       <c r="D80">
-        <v>445.8249784718367</v>
+        <v>441.3149781178251</v>
       </c>
       <c r="E80">
-        <v>899.7700000000001</v>
+        <v>916.4350000000001</v>
       </c>
       <c r="F80">
-        <v>1299.87</v>
+        <v>1316.535</v>
       </c>
       <c r="G80">
         <v>103.6</v>
@@ -7853,37 +7853,37 @@
         <v>104.3</v>
       </c>
       <c r="M80">
-        <v>306.5093460000001</v>
+        <v>310.438953</v>
       </c>
       <c r="N80">
-        <v>-202.2093460000001</v>
+        <v>-206.138953</v>
       </c>
       <c r="O80">
-        <v>-50.55233650000002</v>
+        <v>-51.53473825000001</v>
       </c>
       <c r="P80">
-        <v>-151.6570095</v>
+        <v>-154.60421475</v>
       </c>
       <c r="Q80">
-        <v>-108.7570095</v>
+        <v>-111.70421475</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2252114880197423</v>
+        <v>0.2337548922111586</v>
       </c>
       <c r="T80">
-        <v>3.497063839931819</v>
+        <v>3.663590689452383</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08507081542629369</v>
+        <v>0.08399396966140391</v>
       </c>
       <c r="W80">
-        <v>0.21574030172248</v>
+        <v>0.215994221953841</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3402832617051748</v>
+        <v>0.3359758786456156</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2197239627078777</v>
+        <v>0.2216239627078777</v>
       </c>
       <c r="C81">
-        <v>-771.6200218821749</v>
+        <v>-792.7046890213601</v>
       </c>
       <c r="D81">
-        <v>441.3149781178251</v>
+        <v>436.89531097864</v>
       </c>
       <c r="E81">
-        <v>916.4350000000001</v>
+        <v>933.1</v>
       </c>
       <c r="F81">
-        <v>1316.535</v>
+        <v>1333.2</v>
       </c>
       <c r="G81">
         <v>103.6</v>
@@ -7935,37 +7935,37 @@
         <v>104.3</v>
       </c>
       <c r="M81">
-        <v>310.438953</v>
+        <v>314.36856</v>
       </c>
       <c r="N81">
-        <v>-206.138953</v>
+        <v>-210.06856</v>
       </c>
       <c r="O81">
-        <v>-51.53473825000001</v>
+        <v>-52.51714</v>
       </c>
       <c r="P81">
-        <v>-154.60421475</v>
+        <v>-157.55142</v>
       </c>
       <c r="Q81">
-        <v>-111.70421475</v>
+        <v>-114.65142</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2337548922111586</v>
+        <v>0.2431526368217166</v>
       </c>
       <c r="T81">
-        <v>3.663590689452383</v>
+        <v>3.846770223925003</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08399396966140391</v>
+        <v>0.08294404504063636</v>
       </c>
       <c r="W81">
-        <v>0.215994221953841</v>
+        <v>0.216241794179418</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3359758786456156</v>
+        <v>0.3317761801625455</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2216239627078777</v>
+        <v>0.2235239627078777</v>
       </c>
       <c r="C82">
-        <v>-792.7046890213601</v>
+        <v>-813.7017100337335</v>
       </c>
       <c r="D82">
-        <v>436.89531097864</v>
+        <v>432.5632899662665</v>
       </c>
       <c r="E82">
-        <v>933.1</v>
+        <v>949.765</v>
       </c>
       <c r="F82">
-        <v>1333.2</v>
+        <v>1349.865</v>
       </c>
       <c r="G82">
         <v>103.6</v>
@@ -8017,37 +8017,37 @@
         <v>104.3</v>
       </c>
       <c r="M82">
-        <v>314.36856</v>
+        <v>318.298167</v>
       </c>
       <c r="N82">
-        <v>-210.06856</v>
+        <v>-213.9981670000001</v>
       </c>
       <c r="O82">
-        <v>-52.51714</v>
+        <v>-53.49954175000001</v>
       </c>
       <c r="P82">
-        <v>-157.55142</v>
+        <v>-160.49862525</v>
       </c>
       <c r="Q82">
-        <v>-114.65142</v>
+        <v>-117.59862525</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2431526368217166</v>
+        <v>0.2535396177070701</v>
       </c>
       <c r="T82">
-        <v>3.846770223925003</v>
+        <v>4.049231814657897</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08294404504063636</v>
+        <v>0.08192004448457912</v>
       </c>
       <c r="W82">
-        <v>0.216241794179418</v>
+        <v>0.2164832535105362</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3317761801625455</v>
+        <v>0.3276801779383165</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2235239627078777</v>
+        <v>0.2254239627078777</v>
       </c>
       <c r="C83">
-        <v>-813.7017100337335</v>
+        <v>-834.6136664787472</v>
       </c>
       <c r="D83">
-        <v>432.5632899662665</v>
+        <v>428.316333521253</v>
       </c>
       <c r="E83">
-        <v>949.765</v>
+        <v>966.4300000000002</v>
       </c>
       <c r="F83">
-        <v>1349.865</v>
+        <v>1366.53</v>
       </c>
       <c r="G83">
         <v>103.6</v>
@@ -8099,37 +8099,37 @@
         <v>104.3</v>
       </c>
       <c r="M83">
-        <v>318.298167</v>
+        <v>322.2277740000001</v>
       </c>
       <c r="N83">
-        <v>-213.9981670000001</v>
+        <v>-217.9277740000001</v>
       </c>
       <c r="O83">
-        <v>-53.49954175000001</v>
+        <v>-54.48194350000002</v>
       </c>
       <c r="P83">
-        <v>-160.49862525</v>
+        <v>-163.4458305000001</v>
       </c>
       <c r="Q83">
-        <v>-117.59862525</v>
+        <v>-120.5458305000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2535396177070701</v>
+        <v>0.2650807075796851</v>
       </c>
       <c r="T83">
-        <v>4.049231814657897</v>
+        <v>4.274189137694448</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08192004448457912</v>
+        <v>0.08092101955184033</v>
       </c>
       <c r="W83">
-        <v>0.2164832535105362</v>
+        <v>0.216718823589676</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3276801779383165</v>
+        <v>0.3236840782073613</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2254239627078777</v>
+        <v>0.2273239627078777</v>
       </c>
       <c r="C84">
-        <v>-834.6136664787472</v>
+        <v>-855.4430395173772</v>
       </c>
       <c r="D84">
-        <v>428.316333521253</v>
+        <v>424.1519604826229</v>
       </c>
       <c r="E84">
-        <v>966.4300000000002</v>
+        <v>983.0950000000001</v>
       </c>
       <c r="F84">
-        <v>1366.53</v>
+        <v>1383.195</v>
       </c>
       <c r="G84">
         <v>103.6</v>
@@ -8181,37 +8181,37 @@
         <v>104.3</v>
       </c>
       <c r="M84">
-        <v>322.2277740000001</v>
+        <v>326.157381</v>
       </c>
       <c r="N84">
-        <v>-217.9277740000001</v>
+        <v>-221.8573810000001</v>
       </c>
       <c r="O84">
-        <v>-54.48194350000002</v>
+        <v>-55.46434525000002</v>
       </c>
       <c r="P84">
-        <v>-163.4458305000001</v>
+        <v>-166.3930357500001</v>
       </c>
       <c r="Q84">
-        <v>-120.5458305000001</v>
+        <v>-123.49303575</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2650807075796851</v>
+        <v>0.2779795727314313</v>
       </c>
       <c r="T84">
-        <v>4.274189137694448</v>
+        <v>4.525612028147063</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08092101955184033</v>
+        <v>0.07994606750904709</v>
       </c>
       <c r="W84">
-        <v>0.216718823589676</v>
+        <v>0.2169487172813667</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3236840782073613</v>
+        <v>0.3197842700361884</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2273239627078777</v>
+        <v>0.2292239627078777</v>
       </c>
       <c r="C85">
-        <v>-855.4430395173772</v>
+        <v>-876.1922147458313</v>
       </c>
       <c r="D85">
-        <v>424.1519604826229</v>
+        <v>420.0677852541689</v>
       </c>
       <c r="E85">
-        <v>983.0950000000001</v>
+        <v>999.7600000000001</v>
       </c>
       <c r="F85">
-        <v>1383.195</v>
+        <v>1399.86</v>
       </c>
       <c r="G85">
         <v>103.6</v>
@@ -8263,37 +8263,37 @@
         <v>104.3</v>
       </c>
       <c r="M85">
-        <v>326.157381</v>
+        <v>330.086988</v>
       </c>
       <c r="N85">
-        <v>-221.8573810000001</v>
+        <v>-225.786988</v>
       </c>
       <c r="O85">
-        <v>-55.46434525000002</v>
+        <v>-56.44674700000001</v>
       </c>
       <c r="P85">
-        <v>-166.3930357500001</v>
+        <v>-169.340241</v>
       </c>
       <c r="Q85">
-        <v>-123.49303575</v>
+        <v>-126.440241</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2779795727314313</v>
+        <v>0.2924907960271458</v>
       </c>
       <c r="T85">
-        <v>4.525612028147063</v>
+        <v>4.808462779906255</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07994606750904709</v>
+        <v>0.07899432861012987</v>
       </c>
       <c r="W85">
-        <v>0.2169487172813667</v>
+        <v>0.2171731373137314</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3197842700361884</v>
+        <v>0.3159773144405195</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2292239627078777</v>
+        <v>0.2311239627078776</v>
       </c>
       <c r="C86">
-        <v>-876.1922147458307</v>
+        <v>-896.863486752647</v>
       </c>
       <c r="D86">
-        <v>420.0677852541692</v>
+        <v>416.0615132473529</v>
       </c>
       <c r="E86">
-        <v>999.7599999999999</v>
+        <v>1016.425</v>
       </c>
       <c r="F86">
-        <v>1399.86</v>
+        <v>1416.525</v>
       </c>
       <c r="G86">
         <v>103.6</v>
@@ -8345,37 +8345,37 @@
         <v>104.3</v>
       </c>
       <c r="M86">
-        <v>330.086988</v>
+        <v>334.016595</v>
       </c>
       <c r="N86">
-        <v>-225.786988</v>
+        <v>-229.716595</v>
       </c>
       <c r="O86">
-        <v>-56.44674699999999</v>
+        <v>-57.42914875</v>
       </c>
       <c r="P86">
-        <v>-169.340241</v>
+        <v>-172.28744625</v>
       </c>
       <c r="Q86">
-        <v>-126.440241</v>
+        <v>-129.38744625</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2924907960271456</v>
+        <v>0.308936849095622</v>
       </c>
       <c r="T86">
-        <v>4.808462779906251</v>
+        <v>5.129026965233335</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07899432861012988</v>
+        <v>0.07806498356765776</v>
       </c>
       <c r="W86">
-        <v>0.2171731373137314</v>
+        <v>0.2173922768747463</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3159773144405196</v>
+        <v>0.312259934270631</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2311239627078776</v>
+        <v>0.2330239627078777</v>
       </c>
       <c r="C87">
-        <v>-896.863486752647</v>
+        <v>-917.4590634174933</v>
       </c>
       <c r="D87">
-        <v>416.0615132473529</v>
+        <v>412.1309365825068</v>
       </c>
       <c r="E87">
-        <v>1016.425</v>
+        <v>1033.09</v>
       </c>
       <c r="F87">
-        <v>1416.525</v>
+        <v>1433.19</v>
       </c>
       <c r="G87">
         <v>103.6</v>
@@ -8427,37 +8427,37 @@
         <v>104.3</v>
       </c>
       <c r="M87">
-        <v>334.016595</v>
+        <v>337.946202</v>
       </c>
       <c r="N87">
-        <v>-229.716595</v>
+        <v>-233.646202</v>
       </c>
       <c r="O87">
-        <v>-57.42914875</v>
+        <v>-58.41155050000001</v>
       </c>
       <c r="P87">
-        <v>-172.28744625</v>
+        <v>-175.2346515</v>
       </c>
       <c r="Q87">
-        <v>-129.38744625</v>
+        <v>-132.3346515</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.308936849095622</v>
+        <v>0.3277323383167379</v>
       </c>
       <c r="T87">
-        <v>5.129026965233335</v>
+        <v>5.495386034178574</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07806498356765776</v>
+        <v>0.07715725120059196</v>
       </c>
       <c r="W87">
-        <v>0.2173922768747463</v>
+        <v>0.2176063201669004</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.312259934270631</v>
+        <v>0.3086290048023679</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2330239627078777</v>
+        <v>0.2349239627078777</v>
       </c>
       <c r="C88">
-        <v>-917.4590634174933</v>
+        <v>-937.981069968571</v>
       </c>
       <c r="D88">
-        <v>412.1309365825068</v>
+        <v>408.273930031429</v>
       </c>
       <c r="E88">
-        <v>1033.09</v>
+        <v>1049.755</v>
       </c>
       <c r="F88">
-        <v>1433.19</v>
+        <v>1449.855</v>
       </c>
       <c r="G88">
         <v>103.6</v>
@@ -8509,37 +8509,37 @@
         <v>104.3</v>
       </c>
       <c r="M88">
-        <v>337.946202</v>
+        <v>341.875809</v>
       </c>
       <c r="N88">
-        <v>-233.646202</v>
+        <v>-237.575809</v>
       </c>
       <c r="O88">
-        <v>-58.41155050000001</v>
+        <v>-59.39395225000001</v>
       </c>
       <c r="P88">
-        <v>-175.2346515</v>
+        <v>-178.18185675</v>
       </c>
       <c r="Q88">
-        <v>-132.3346515</v>
+        <v>-135.28185675</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3277323383167379</v>
+        <v>0.3494194412641792</v>
       </c>
       <c r="T88">
-        <v>5.495386034178574</v>
+        <v>5.918108036807694</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07715725120059196</v>
+        <v>0.07627038624426333</v>
       </c>
       <c r="W88">
-        <v>0.2176063201669004</v>
+        <v>0.2178154429236027</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3086290048023679</v>
+        <v>0.3050815449770533</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2349239627078777</v>
+        <v>0.2368239627078777</v>
       </c>
       <c r="C89">
-        <v>-937.981069968571</v>
+        <v>-958.4315528143077</v>
       </c>
       <c r="D89">
-        <v>408.273930031429</v>
+        <v>404.4884471856923</v>
       </c>
       <c r="E89">
-        <v>1049.755</v>
+        <v>1066.42</v>
       </c>
       <c r="F89">
-        <v>1449.855</v>
+        <v>1466.52</v>
       </c>
       <c r="G89">
         <v>103.6</v>
@@ -8591,37 +8591,37 @@
         <v>104.3</v>
       </c>
       <c r="M89">
-        <v>341.875809</v>
+        <v>345.805416</v>
       </c>
       <c r="N89">
-        <v>-237.575809</v>
+        <v>-241.5054160000001</v>
       </c>
       <c r="O89">
-        <v>-59.39395225000001</v>
+        <v>-60.37635400000001</v>
       </c>
       <c r="P89">
-        <v>-178.18185675</v>
+        <v>-181.129062</v>
       </c>
       <c r="Q89">
-        <v>-135.28185675</v>
+        <v>-138.229062</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3494194412641792</v>
+        <v>0.3747210613695275</v>
       </c>
       <c r="T89">
-        <v>5.918108036807694</v>
+        <v>6.41128370654167</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07627038624426333</v>
+        <v>0.07540367730966942</v>
       </c>
       <c r="W89">
-        <v>0.2178154429236027</v>
+        <v>0.2180198128903799</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3050815449770533</v>
+        <v>0.3016147092386776</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2368239627078777</v>
+        <v>0.2387239627078777</v>
       </c>
       <c r="C90">
-        <v>-958.4315528143077</v>
+        <v>-978.8124831638389</v>
       </c>
       <c r="D90">
-        <v>404.4884471856923</v>
+        <v>400.7725168361611</v>
       </c>
       <c r="E90">
-        <v>1066.42</v>
+        <v>1083.085</v>
       </c>
       <c r="F90">
-        <v>1466.52</v>
+        <v>1483.185</v>
       </c>
       <c r="G90">
         <v>103.6</v>
@@ -8673,37 +8673,37 @@
         <v>104.3</v>
       </c>
       <c r="M90">
-        <v>345.805416</v>
+        <v>349.735023</v>
       </c>
       <c r="N90">
-        <v>-241.5054160000001</v>
+        <v>-245.435023</v>
       </c>
       <c r="O90">
-        <v>-60.37635400000001</v>
+        <v>-61.35875575000001</v>
       </c>
       <c r="P90">
-        <v>-181.129062</v>
+        <v>-184.07626725</v>
       </c>
       <c r="Q90">
-        <v>-138.229062</v>
+        <v>-141.17626725</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3747210613695275</v>
+        <v>0.4046229760394845</v>
       </c>
       <c r="T90">
-        <v>6.41128370654167</v>
+        <v>6.994127679863639</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07540367730966942</v>
+        <v>0.07455644498034729</v>
       </c>
       <c r="W90">
-        <v>0.2180198128903799</v>
+        <v>0.2182195902736341</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3016147092386776</v>
+        <v>0.2982257799213892</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2387239627078777</v>
+        <v>0.2406239627078777</v>
       </c>
       <c r="C91">
-        <v>-978.8124831638389</v>
+        <v>-999.1257604497458</v>
       </c>
       <c r="D91">
-        <v>400.7725168361611</v>
+        <v>397.1242395502543</v>
       </c>
       <c r="E91">
-        <v>1083.085</v>
+        <v>1099.75</v>
       </c>
       <c r="F91">
-        <v>1483.185</v>
+        <v>1499.85</v>
       </c>
       <c r="G91">
         <v>103.6</v>
@@ -8755,37 +8755,37 @@
         <v>104.3</v>
       </c>
       <c r="M91">
-        <v>349.735023</v>
+        <v>353.66463</v>
       </c>
       <c r="N91">
-        <v>-245.435023</v>
+        <v>-249.3646300000001</v>
       </c>
       <c r="O91">
-        <v>-61.35875575000001</v>
+        <v>-62.34115750000002</v>
       </c>
       <c r="P91">
-        <v>-184.07626725</v>
+        <v>-187.0234725000001</v>
       </c>
       <c r="Q91">
-        <v>-141.17626725</v>
+        <v>-144.1234725</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4046229760394845</v>
+        <v>0.4405052736434331</v>
       </c>
       <c r="T91">
-        <v>6.994127679863639</v>
+        <v>7.693540447850004</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07455644498034729</v>
+        <v>0.0737280400361212</v>
       </c>
       <c r="W91">
-        <v>0.2182195902736341</v>
+        <v>0.2184149281594826</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2982257799213892</v>
+        <v>0.2949121601444848</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2406239627078777</v>
+        <v>0.2425239627078777</v>
       </c>
       <c r="C92">
-        <v>-999.1257604497458</v>
+        <v>-1019.373215565535</v>
       </c>
       <c r="D92">
-        <v>397.1242395502543</v>
+        <v>393.5417844344651</v>
       </c>
       <c r="E92">
-        <v>1099.75</v>
+        <v>1116.415</v>
       </c>
       <c r="F92">
-        <v>1499.85</v>
+        <v>1516.515</v>
       </c>
       <c r="G92">
         <v>103.6</v>
@@ -8837,37 +8837,37 @@
         <v>104.3</v>
       </c>
       <c r="M92">
-        <v>353.66463</v>
+        <v>357.594237</v>
       </c>
       <c r="N92">
-        <v>-249.3646300000001</v>
+        <v>-253.294237</v>
       </c>
       <c r="O92">
-        <v>-62.34115750000002</v>
+        <v>-63.32355925000001</v>
       </c>
       <c r="P92">
-        <v>-187.0234725000001</v>
+        <v>-189.97067775</v>
       </c>
       <c r="Q92">
-        <v>-144.1234725</v>
+        <v>-147.07067775</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4405052736434331</v>
+        <v>0.4843614151593702</v>
       </c>
       <c r="T92">
-        <v>7.693540447850004</v>
+        <v>8.548378275388895</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0737280400361212</v>
+        <v>0.07291784179396603</v>
       </c>
       <c r="W92">
-        <v>0.2184149281594826</v>
+        <v>0.2186059729049828</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2949121601444848</v>
+        <v>0.2916713671758642</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2425239627078777</v>
+        <v>0.2444239627078776</v>
       </c>
       <c r="C93">
-        <v>-1019.373215565535</v>
+        <v>-1039.556613929453</v>
       </c>
       <c r="D93">
-        <v>393.5417844344651</v>
+        <v>390.0233860705471</v>
       </c>
       <c r="E93">
-        <v>1116.415</v>
+        <v>1133.08</v>
       </c>
       <c r="F93">
-        <v>1516.515</v>
+        <v>1533.18</v>
       </c>
       <c r="G93">
         <v>103.6</v>
@@ -8919,37 +8919,37 @@
         <v>104.3</v>
       </c>
       <c r="M93">
-        <v>357.594237</v>
+        <v>361.5238440000001</v>
       </c>
       <c r="N93">
-        <v>-253.294237</v>
+        <v>-257.2238440000001</v>
       </c>
       <c r="O93">
-        <v>-63.32355925000001</v>
+        <v>-64.30596100000002</v>
       </c>
       <c r="P93">
-        <v>-189.97067775</v>
+        <v>-192.9178830000001</v>
       </c>
       <c r="Q93">
-        <v>-147.07067775</v>
+        <v>-150.0178830000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4843614151593702</v>
+        <v>0.5391815920542915</v>
       </c>
       <c r="T93">
-        <v>8.548378275388895</v>
+        <v>9.616925559812509</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07291784179396603</v>
+        <v>0.07212525655707509</v>
       </c>
       <c r="W93">
-        <v>0.2186059729049828</v>
+        <v>0.2187928645038417</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2916713671758642</v>
+        <v>0.2885010262283003</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2444239627078776</v>
+        <v>0.2463239627078777</v>
       </c>
       <c r="C94">
-        <v>-1039.556613929453</v>
+        <v>-1059.677658385407</v>
       </c>
       <c r="D94">
-        <v>390.0233860705471</v>
+        <v>386.5673416145932</v>
       </c>
       <c r="E94">
-        <v>1133.08</v>
+        <v>1149.745</v>
       </c>
       <c r="F94">
-        <v>1533.18</v>
+        <v>1549.845</v>
       </c>
       <c r="G94">
         <v>103.6</v>
@@ -9001,37 +9001,37 @@
         <v>104.3</v>
       </c>
       <c r="M94">
-        <v>361.5238440000001</v>
+        <v>365.453451</v>
       </c>
       <c r="N94">
-        <v>-257.2238440000001</v>
+        <v>-261.153451</v>
       </c>
       <c r="O94">
-        <v>-64.30596100000002</v>
+        <v>-65.28836275</v>
       </c>
       <c r="P94">
-        <v>-192.9178830000001</v>
+        <v>-195.86508825</v>
       </c>
       <c r="Q94">
-        <v>-150.0178830000001</v>
+        <v>-152.96508825</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5391815920542915</v>
+        <v>0.6096646766334761</v>
       </c>
       <c r="T94">
-        <v>9.616925559812509</v>
+        <v>10.99077206835716</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07212525655707509</v>
+        <v>0.07134971616398826</v>
       </c>
       <c r="W94">
-        <v>0.2187928645038417</v>
+        <v>0.2189757369285316</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2885010262283003</v>
+        <v>0.2853988646559531</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2463239627078777</v>
+        <v>0.2482239627078777</v>
       </c>
       <c r="C95">
-        <v>-1059.677658385407</v>
+        <v>-1079.737991951007</v>
       </c>
       <c r="D95">
-        <v>386.5673416145932</v>
+        <v>383.1720080489926</v>
       </c>
       <c r="E95">
-        <v>1149.745</v>
+        <v>1166.41</v>
       </c>
       <c r="F95">
-        <v>1549.845</v>
+        <v>1566.51</v>
       </c>
       <c r="G95">
         <v>103.6</v>
@@ -9083,37 +9083,37 @@
         <v>104.3</v>
       </c>
       <c r="M95">
-        <v>365.453451</v>
+        <v>369.383058</v>
       </c>
       <c r="N95">
-        <v>-261.153451</v>
+        <v>-265.0830580000001</v>
       </c>
       <c r="O95">
-        <v>-65.28836275</v>
+        <v>-66.27076450000001</v>
       </c>
       <c r="P95">
-        <v>-195.86508825</v>
+        <v>-198.8122935</v>
       </c>
       <c r="Q95">
-        <v>-152.96508825</v>
+        <v>-155.9122935</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6096646766334761</v>
+        <v>0.7036421227390557</v>
       </c>
       <c r="T95">
-        <v>10.99077206835716</v>
+        <v>12.82256741308335</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07134971616398826</v>
+        <v>0.07059067663032882</v>
       </c>
       <c r="W95">
-        <v>0.2189757369285316</v>
+        <v>0.2191547184505685</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2853988646559531</v>
+        <v>0.2823627065213152</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2482239627078777</v>
+        <v>0.2501239627078777</v>
       </c>
       <c r="C96">
-        <v>-1079.737991951007</v>
+        <v>-1099.739200422052</v>
       </c>
       <c r="D96">
-        <v>383.1720080489926</v>
+        <v>379.8357995779482</v>
       </c>
       <c r="E96">
-        <v>1166.41</v>
+        <v>1183.075</v>
       </c>
       <c r="F96">
-        <v>1566.51</v>
+        <v>1583.175</v>
       </c>
       <c r="G96">
         <v>103.6</v>
@@ -9165,37 +9165,37 @@
         <v>104.3</v>
       </c>
       <c r="M96">
-        <v>369.383058</v>
+        <v>373.312665</v>
       </c>
       <c r="N96">
-        <v>-265.0830580000001</v>
+        <v>-269.0126650000001</v>
       </c>
       <c r="O96">
-        <v>-66.27076450000001</v>
+        <v>-67.25316625000002</v>
       </c>
       <c r="P96">
-        <v>-198.8122935</v>
+        <v>-201.7594987500001</v>
       </c>
       <c r="Q96">
-        <v>-155.9122935</v>
+        <v>-158.8594987500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7036421227390557</v>
+        <v>0.8352105472868672</v>
       </c>
       <c r="T96">
-        <v>12.82256741308335</v>
+        <v>15.38708089570003</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07059067663032882</v>
+        <v>0.06984761687632535</v>
       </c>
       <c r="W96">
-        <v>0.2191547184505685</v>
+        <v>0.2193299319405625</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2823627065213152</v>
+        <v>0.2793904675053014</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2501239627078777</v>
+        <v>0.2520239627078777</v>
       </c>
       <c r="C97">
-        <v>-1099.739200422052</v>
+        <v>-1119.682814842121</v>
       </c>
       <c r="D97">
-        <v>379.8357995779482</v>
+        <v>376.5571851578788</v>
       </c>
       <c r="E97">
-        <v>1183.075</v>
+        <v>1199.74</v>
       </c>
       <c r="F97">
-        <v>1583.175</v>
+        <v>1599.84</v>
       </c>
       <c r="G97">
         <v>103.6</v>
@@ -9247,37 +9247,37 @@
         <v>104.3</v>
       </c>
       <c r="M97">
-        <v>373.312665</v>
+        <v>377.2422720000001</v>
       </c>
       <c r="N97">
-        <v>-269.0126650000001</v>
+        <v>-272.9422720000001</v>
       </c>
       <c r="O97">
-        <v>-67.25316625000002</v>
+        <v>-68.23556800000003</v>
       </c>
       <c r="P97">
-        <v>-201.7594987500001</v>
+        <v>-204.7067040000001</v>
       </c>
       <c r="Q97">
-        <v>-158.8594987500001</v>
+        <v>-161.8067040000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8352105472868672</v>
+        <v>1.032563184108584</v>
       </c>
       <c r="T97">
-        <v>15.38708089570003</v>
+        <v>19.23385111962504</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06984761687632535</v>
+        <v>0.06912003753386363</v>
       </c>
       <c r="W97">
-        <v>0.2193299319405625</v>
+        <v>0.219501495149515</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2793904675053014</v>
+        <v>0.2764801501354545</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2520239627078777</v>
+        <v>0.2539239627078776</v>
       </c>
       <c r="C98">
-        <v>-1119.682814842121</v>
+        <v>-1139.570313845371</v>
       </c>
       <c r="D98">
-        <v>376.5571851578788</v>
+        <v>373.3346861546289</v>
       </c>
       <c r="E98">
-        <v>1199.74</v>
+        <v>1216.405</v>
       </c>
       <c r="F98">
-        <v>1599.84</v>
+        <v>1616.505</v>
       </c>
       <c r="G98">
         <v>103.6</v>
@@ -9329,37 +9329,37 @@
         <v>104.3</v>
       </c>
       <c r="M98">
-        <v>377.242272</v>
+        <v>381.171879</v>
       </c>
       <c r="N98">
-        <v>-272.942272</v>
+        <v>-276.871879</v>
       </c>
       <c r="O98">
-        <v>-68.235568</v>
+        <v>-69.21796975000001</v>
       </c>
       <c r="P98">
-        <v>-204.706704</v>
+        <v>-207.65390925</v>
       </c>
       <c r="Q98">
-        <v>-161.806704</v>
+        <v>-164.75390925</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.032563184108582</v>
+        <v>1.361484245478109</v>
       </c>
       <c r="T98">
-        <v>19.23385111962499</v>
+        <v>25.64513482616666</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06912003753386363</v>
+        <v>0.06840745982732896</v>
       </c>
       <c r="W98">
-        <v>0.219501495149515</v>
+        <v>0.2196695209727158</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2764801501354546</v>
+        <v>0.2736298393093157</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2539239627078776</v>
+        <v>0.2558239627078777</v>
       </c>
       <c r="C99">
-        <v>-1139.570313845371</v>
+        <v>-1159.40312588005</v>
       </c>
       <c r="D99">
-        <v>373.3346861546289</v>
+        <v>370.1668741199505</v>
       </c>
       <c r="E99">
-        <v>1216.405</v>
+        <v>1233.07</v>
       </c>
       <c r="F99">
-        <v>1616.505</v>
+        <v>1633.17</v>
       </c>
       <c r="G99">
         <v>103.6</v>
@@ -9411,37 +9411,37 @@
         <v>104.3</v>
       </c>
       <c r="M99">
-        <v>381.171879</v>
+        <v>385.101486</v>
       </c>
       <c r="N99">
-        <v>-276.871879</v>
+        <v>-280.8014860000001</v>
       </c>
       <c r="O99">
-        <v>-69.21796975000001</v>
+        <v>-70.20037150000002</v>
       </c>
       <c r="P99">
-        <v>-207.65390925</v>
+        <v>-210.6011145000001</v>
       </c>
       <c r="Q99">
-        <v>-164.75390925</v>
+        <v>-167.7011145</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.361484245478109</v>
+        <v>2.019326368217164</v>
       </c>
       <c r="T99">
-        <v>25.64513482616666</v>
+        <v>38.46770223924999</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06840745982732896</v>
+        <v>0.06770942452296846</v>
       </c>
       <c r="W99">
-        <v>0.2196695209727158</v>
+        <v>0.219834117697484</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2736298393093157</v>
+        <v>0.2708376980918737</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2558239627078777</v>
+        <v>0.2577239627078777</v>
       </c>
       <c r="C100">
-        <v>-1159.40312588005</v>
+        <v>-1179.182631319763</v>
       </c>
       <c r="D100">
-        <v>370.1668741199505</v>
+        <v>367.0523686802367</v>
       </c>
       <c r="E100">
-        <v>1233.07</v>
+        <v>1249.735</v>
       </c>
       <c r="F100">
-        <v>1633.17</v>
+        <v>1649.835</v>
       </c>
       <c r="G100">
         <v>103.6</v>
@@ -9493,37 +9493,37 @@
         <v>104.3</v>
       </c>
       <c r="M100">
-        <v>385.101486</v>
+        <v>389.031093</v>
       </c>
       <c r="N100">
-        <v>-280.8014860000001</v>
+        <v>-284.731093</v>
       </c>
       <c r="O100">
-        <v>-70.20037150000002</v>
+        <v>-71.18277325</v>
       </c>
       <c r="P100">
-        <v>-210.6011145000001</v>
+        <v>-213.54831975</v>
       </c>
       <c r="Q100">
-        <v>-167.7011145</v>
+        <v>-170.64831975</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.019326368217164</v>
+        <v>3.992852736434327</v>
       </c>
       <c r="T100">
-        <v>38.46770223924999</v>
+        <v>76.93540447849998</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06770942452296846</v>
+        <v>0.06702549094192838</v>
       </c>
       <c r="W100">
-        <v>0.219834117697484</v>
+        <v>0.2199953892358933</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2708376980918737</v>
+        <v>0.2681019637677136</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2577239627078777</v>
-      </c>
-      <c r="C101">
-        <v>-1179.182631319763</v>
-      </c>
-      <c r="D101">
-        <v>367.0523686802367</v>
-      </c>
-      <c r="E101">
-        <v>1249.735</v>
-      </c>
-      <c r="F101">
-        <v>1649.835</v>
-      </c>
-      <c r="G101">
-        <v>103.6</v>
-      </c>
-      <c r="H101">
-        <v>1266.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>147.2</v>
-      </c>
-      <c r="K101">
-        <v>42.9</v>
-      </c>
-      <c r="L101">
-        <v>104.3</v>
-      </c>
-      <c r="M101">
-        <v>389.031093</v>
-      </c>
-      <c r="N101">
-        <v>-284.731093</v>
-      </c>
-      <c r="O101">
-        <v>-71.18277325</v>
-      </c>
-      <c r="P101">
-        <v>-213.54831975</v>
-      </c>
-      <c r="Q101">
-        <v>-170.64831975</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.992852736434327</v>
-      </c>
-      <c r="T101">
-        <v>76.93540447849998</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06702549094192838</v>
-      </c>
-      <c r="W101">
-        <v>0.2199953892358933</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2681019637677136</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
